--- a/jpcore-r4/develop-kohetest/StructureDefinition-jp-encounter.xlsx
+++ b/jpcore-r4/develop-kohetest/StructureDefinition-jp-encounter.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2716" uniqueCount="473">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2716" uniqueCount="472">
   <si>
     <t>Property</t>
   </si>
@@ -460,15 +460,11 @@
     <t>associatedEncounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {encounter-associatedEncounter}
+    <t xml:space="preserve">Extension {encounter-associatedEncounter|latest}
 </t>
   </si>
   <si>
     <t>関連するEncounter</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>Encounter.modifierExtension</t>
@@ -2953,7 +2949,7 @@
         <v>81</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>81</v>
@@ -2970,14 +2966,14 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
@@ -2999,16 +2995,16 @@
         <v>134</v>
       </c>
       <c r="L11" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="M11" t="s" s="2">
         <v>148</v>
       </c>
-      <c r="M11" t="s" s="2">
+      <c r="N11" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="N11" t="s" s="2">
+      <c r="O11" t="s" s="2">
         <v>150</v>
-      </c>
-      <c r="O11" t="s" s="2">
-        <v>151</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>81</v>
@@ -3057,7 +3053,7 @@
         <v>81</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>79</v>
@@ -3086,10 +3082,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3112,13 +3108,13 @@
         <v>90</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="L12" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="L12" t="s" s="2">
+      <c r="M12" t="s" s="2">
         <v>155</v>
-      </c>
-      <c r="M12" t="s" s="2">
-        <v>156</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -3169,7 +3165,7 @@
         <v>81</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>79</v>
@@ -3184,24 +3180,24 @@
         <v>101</v>
       </c>
       <c r="AK12" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="AL12" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="AL12" t="s" s="2">
+      <c r="AM12" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="AM12" t="s" s="2">
+      <c r="AN12" t="s" s="2">
         <v>159</v>
-      </c>
-      <c r="AN12" t="s" s="2">
-        <v>160</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3227,13 +3223,13 @@
         <v>109</v>
       </c>
       <c r="L13" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="M13" t="s" s="2">
         <v>162</v>
       </c>
-      <c r="M13" t="s" s="2">
+      <c r="N13" t="s" s="2">
         <v>163</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>164</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3259,14 +3255,14 @@
         <v>81</v>
       </c>
       <c r="X13" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="Y13" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="Y13" t="s" s="2">
+      <c r="Z13" t="s" s="2">
         <v>166</v>
       </c>
-      <c r="Z13" t="s" s="2">
-        <v>167</v>
-      </c>
       <c r="AA13" t="s" s="2">
         <v>81</v>
       </c>
@@ -3283,7 +3279,7 @@
         <v>81</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>89</v>
@@ -3298,24 +3294,24 @@
         <v>101</v>
       </c>
       <c r="AK13" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AL13" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="AL13" t="s" s="2">
+      <c r="AM13" t="s" s="2">
         <v>169</v>
       </c>
-      <c r="AM13" t="s" s="2">
+      <c r="AN13" t="s" s="2">
         <v>170</v>
-      </c>
-      <c r="AN13" t="s" s="2">
-        <v>171</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3338,16 +3334,16 @@
         <v>81</v>
       </c>
       <c r="K14" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="L14" t="s" s="2">
         <v>173</v>
       </c>
-      <c r="L14" t="s" s="2">
+      <c r="M14" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="M14" t="s" s="2">
+      <c r="N14" t="s" s="2">
         <v>175</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>176</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3397,7 +3393,7 @@
         <v>81</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>79</v>
@@ -3415,7 +3411,7 @@
         <v>81</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AM14" t="s" s="2">
         <v>81</v>
@@ -3426,10 +3422,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3452,13 +3448,13 @@
         <v>81</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="L15" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="L15" t="s" s="2">
+      <c r="M15" t="s" s="2">
         <v>180</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>181</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -3509,7 +3505,7 @@
         <v>81</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>79</v>
@@ -3527,7 +3523,7 @@
         <v>81</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>81</v>
@@ -3538,14 +3534,14 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3567,13 +3563,13 @@
         <v>134</v>
       </c>
       <c r="L16" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="M16" t="s" s="2">
         <v>184</v>
       </c>
-      <c r="M16" t="s" s="2">
-        <v>185</v>
-      </c>
       <c r="N16" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3623,7 +3619,7 @@
         <v>81</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
@@ -3641,7 +3637,7 @@
         <v>81</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>81</v>
@@ -3652,14 +3648,14 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3681,16 +3677,16 @@
         <v>134</v>
       </c>
       <c r="L17" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="M17" t="s" s="2">
-        <v>190</v>
-      </c>
       <c r="N17" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="O17" t="s" s="2">
         <v>150</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>151</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>81</v>
@@ -3739,7 +3735,7 @@
         <v>81</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -3768,10 +3764,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3797,13 +3793,13 @@
         <v>109</v>
       </c>
       <c r="L18" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="M18" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="N18" t="s" s="2">
         <v>193</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>194</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3829,14 +3825,14 @@
         <v>81</v>
       </c>
       <c r="X18" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="Y18" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="Y18" t="s" s="2">
+      <c r="Z18" t="s" s="2">
         <v>166</v>
       </c>
-      <c r="Z18" t="s" s="2">
-        <v>167</v>
-      </c>
       <c r="AA18" t="s" s="2">
         <v>81</v>
       </c>
@@ -3853,7 +3849,7 @@
         <v>81</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>89</v>
@@ -3871,7 +3867,7 @@
         <v>81</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>81</v>
@@ -3882,10 +3878,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3908,16 +3904,16 @@
         <v>81</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>196</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="M19" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="M19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>199</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3967,7 +3963,7 @@
         <v>81</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>89</v>
@@ -3985,7 +3981,7 @@
         <v>81</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>81</v>
@@ -3996,10 +3992,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4022,16 +4018,16 @@
         <v>90</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="M20" t="s" s="2">
         <v>202</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>204</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4057,14 +4053,14 @@
         <v>81</v>
       </c>
       <c r="X20" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="Y20" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="Y20" t="s" s="2">
+      <c r="Z20" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="Z20" t="s" s="2">
-        <v>207</v>
-      </c>
       <c r="AA20" t="s" s="2">
         <v>81</v>
       </c>
@@ -4081,7 +4077,7 @@
         <v>81</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>89</v>
@@ -4099,21 +4095,21 @@
         <v>81</v>
       </c>
       <c r="AL20" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="AM20" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="AM20" t="s" s="2">
+      <c r="AN20" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="AN20" t="s" s="2">
-        <v>210</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4136,13 +4132,13 @@
         <v>81</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L21" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="M21" t="s" s="2">
         <v>212</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>213</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4193,7 +4189,7 @@
         <v>81</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -4211,7 +4207,7 @@
         <v>81</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>81</v>
@@ -4222,10 +4218,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4248,13 +4244,13 @@
         <v>81</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="L22" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="L22" t="s" s="2">
+      <c r="M22" t="s" s="2">
         <v>180</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>181</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4305,7 +4301,7 @@
         <v>81</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -4323,7 +4319,7 @@
         <v>81</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>81</v>
@@ -4334,14 +4330,14 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -4363,13 +4359,13 @@
         <v>134</v>
       </c>
       <c r="L23" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>184</v>
       </c>
-      <c r="M23" t="s" s="2">
-        <v>185</v>
-      </c>
       <c r="N23" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4419,7 +4415,7 @@
         <v>81</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -4437,7 +4433,7 @@
         <v>81</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>81</v>
@@ -4448,14 +4444,14 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4477,16 +4473,16 @@
         <v>134</v>
       </c>
       <c r="L24" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="M24" t="s" s="2">
-        <v>190</v>
-      </c>
       <c r="N24" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="O24" t="s" s="2">
         <v>150</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>151</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>81</v>
@@ -4535,7 +4531,7 @@
         <v>81</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -4564,10 +4560,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4590,16 +4586,16 @@
         <v>81</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>219</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>220</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4625,14 +4621,14 @@
         <v>81</v>
       </c>
       <c r="X25" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="Y25" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="Y25" t="s" s="2">
+      <c r="Z25" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="Z25" t="s" s="2">
-        <v>207</v>
-      </c>
       <c r="AA25" t="s" s="2">
         <v>81</v>
       </c>
@@ -4649,7 +4645,7 @@
         <v>81</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>89</v>
@@ -4667,7 +4663,7 @@
         <v>81</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>81</v>
@@ -4678,10 +4674,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4704,16 +4700,16 @@
         <v>81</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>222</v>
       </c>
-      <c r="M26" t="s" s="2">
-        <v>223</v>
-      </c>
       <c r="N26" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4763,7 +4759,7 @@
         <v>81</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>89</v>
@@ -4781,7 +4777,7 @@
         <v>81</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>81</v>
@@ -4792,10 +4788,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4818,16 +4814,16 @@
         <v>90</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="L27" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="M27" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>227</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>228</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -4853,14 +4849,14 @@
         <v>81</v>
       </c>
       <c r="X27" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="Y27" t="s" s="2">
         <v>229</v>
       </c>
-      <c r="Y27" t="s" s="2">
+      <c r="Z27" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="Z27" t="s" s="2">
-        <v>231</v>
-      </c>
       <c r="AA27" t="s" s="2">
         <v>81</v>
       </c>
@@ -4877,7 +4873,7 @@
         <v>81</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -4892,24 +4888,24 @@
         <v>101</v>
       </c>
       <c r="AK27" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="AL27" t="s" s="2">
         <v>232</v>
       </c>
-      <c r="AL27" t="s" s="2">
+      <c r="AM27" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="AN27" t="s" s="2">
         <v>233</v>
-      </c>
-      <c r="AM27" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>234</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4932,13 +4928,13 @@
         <v>90</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>236</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>237</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4965,14 +4961,14 @@
         <v>81</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="Y28" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="Z28" t="s" s="2">
         <v>238</v>
       </c>
-      <c r="Z28" t="s" s="2">
-        <v>239</v>
-      </c>
       <c r="AA28" t="s" s="2">
         <v>81</v>
       </c>
@@ -4989,7 +4985,7 @@
         <v>81</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -5004,24 +5000,24 @@
         <v>101</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5044,13 +5040,13 @@
         <v>81</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="L29" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>242</v>
-      </c>
-      <c r="M29" t="s" s="2">
-        <v>243</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5077,14 +5073,14 @@
         <v>81</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="Y29" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="Z29" t="s" s="2">
         <v>243</v>
       </c>
-      <c r="Z29" t="s" s="2">
-        <v>244</v>
-      </c>
       <c r="AA29" t="s" s="2">
         <v>81</v>
       </c>
@@ -5101,7 +5097,7 @@
         <v>81</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -5119,25 +5115,25 @@
         <v>81</v>
       </c>
       <c r="AL29" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="AM29" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="AM29" t="s" s="2">
+      <c r="AN29" t="s" s="2">
         <v>246</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>247</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -5156,16 +5152,16 @@
         <v>90</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="L30" t="s" s="2">
         <v>250</v>
       </c>
-      <c r="L30" t="s" s="2">
+      <c r="M30" t="s" s="2">
         <v>251</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>252</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>253</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5215,7 +5211,7 @@
         <v>81</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -5230,24 +5226,24 @@
         <v>101</v>
       </c>
       <c r="AK30" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="AL30" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="AL30" t="s" s="2">
+      <c r="AM30" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="AM30" t="s" s="2">
+      <c r="AN30" t="s" s="2">
         <v>256</v>
-      </c>
-      <c r="AN30" t="s" s="2">
-        <v>257</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5270,13 +5266,13 @@
         <v>90</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="L31" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="L31" t="s" s="2">
+      <c r="M31" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>261</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5327,7 +5323,7 @@
         <v>81</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -5342,28 +5338,28 @@
         <v>101</v>
       </c>
       <c r="AK31" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="AL31" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="AM31" t="s" s="2">
         <v>262</v>
       </c>
-      <c r="AL31" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="AM31" t="s" s="2">
+      <c r="AN31" t="s" s="2">
         <v>263</v>
-      </c>
-      <c r="AN31" t="s" s="2">
-        <v>264</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5382,13 +5378,13 @@
         <v>81</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>267</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="M32" t="s" s="2">
         <v>268</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>269</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5439,7 +5435,7 @@
         <v>81</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -5454,10 +5450,10 @@
         <v>101</v>
       </c>
       <c r="AK32" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="AL32" t="s" s="2">
         <v>270</v>
-      </c>
-      <c r="AL32" t="s" s="2">
-        <v>271</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>81</v>
@@ -5468,10 +5464,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5494,13 +5490,13 @@
         <v>90</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>273</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>274</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5551,7 +5547,7 @@
         <v>81</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -5566,24 +5562,24 @@
         <v>101</v>
       </c>
       <c r="AK33" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="AL33" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="AL33" t="s" s="2">
+      <c r="AM33" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN33" t="s" s="2">
         <v>276</v>
-      </c>
-      <c r="AM33" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN33" t="s" s="2">
-        <v>277</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5606,13 +5602,13 @@
         <v>81</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="L34" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="L34" t="s" s="2">
+      <c r="M34" t="s" s="2">
         <v>180</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>181</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5663,7 +5659,7 @@
         <v>81</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -5681,7 +5677,7 @@
         <v>81</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>81</v>
@@ -5692,14 +5688,14 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -5721,13 +5717,13 @@
         <v>134</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>184</v>
       </c>
-      <c r="M35" t="s" s="2">
-        <v>185</v>
-      </c>
       <c r="N35" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5777,7 +5773,7 @@
         <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -5795,7 +5791,7 @@
         <v>81</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>81</v>
@@ -5806,14 +5802,14 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -5835,16 +5831,16 @@
         <v>134</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="M36" t="s" s="2">
-        <v>190</v>
-      </c>
       <c r="N36" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="O36" t="s" s="2">
         <v>150</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>151</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>81</v>
@@ -5893,7 +5889,7 @@
         <v>81</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -5922,10 +5918,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5948,16 +5944,16 @@
         <v>90</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="M37" t="s" s="2">
+      <c r="N37" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>284</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -5983,13 +5979,13 @@
         <v>81</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>81</v>
@@ -6007,7 +6003,7 @@
         <v>81</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -6022,24 +6018,24 @@
         <v>101</v>
       </c>
       <c r="AK37" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="AL37" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="AL37" t="s" s="2">
+      <c r="AM37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN37" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="AM37" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN37" t="s" s="2">
-        <v>288</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6062,13 +6058,13 @@
         <v>81</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>290</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>291</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6119,7 +6115,7 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -6137,21 +6133,21 @@
         <v>81</v>
       </c>
       <c r="AL38" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="AM38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN38" t="s" s="2">
         <v>292</v>
-      </c>
-      <c r="AM38" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN38" t="s" s="2">
-        <v>293</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6174,13 +6170,13 @@
         <v>90</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="L39" t="s" s="2">
         <v>295</v>
       </c>
-      <c r="L39" t="s" s="2">
+      <c r="M39" t="s" s="2">
         <v>296</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>297</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6231,7 +6227,7 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -6246,24 +6242,24 @@
         <v>101</v>
       </c>
       <c r="AK39" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="AL39" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="AL39" t="s" s="2">
+      <c r="AM39" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="AM39" t="s" s="2">
+      <c r="AN39" t="s" s="2">
         <v>300</v>
-      </c>
-      <c r="AN39" t="s" s="2">
-        <v>301</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6286,13 +6282,13 @@
         <v>90</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="L40" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="L40" t="s" s="2">
+      <c r="M40" t="s" s="2">
         <v>304</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>305</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6343,7 +6339,7 @@
         <v>81</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -6358,24 +6354,24 @@
         <v>101</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="AL40" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="AM40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN40" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="AM40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN40" t="s" s="2">
-        <v>307</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6398,16 +6394,16 @@
         <v>81</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="M41" t="s" s="2">
+      <c r="N41" t="s" s="2">
         <v>310</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>311</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6457,7 +6453,7 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -6472,24 +6468,24 @@
         <v>101</v>
       </c>
       <c r="AK41" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="AL41" t="s" s="2">
         <v>312</v>
       </c>
-      <c r="AL41" t="s" s="2">
+      <c r="AM41" t="s" s="2">
         <v>313</v>
       </c>
-      <c r="AM41" t="s" s="2">
+      <c r="AN41" t="s" s="2">
         <v>314</v>
-      </c>
-      <c r="AN41" t="s" s="2">
-        <v>315</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6512,16 +6508,16 @@
         <v>81</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="L42" t="s" s="2">
         <v>317</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="M42" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>319</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>320</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6571,7 +6567,7 @@
         <v>81</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -6586,28 +6582,28 @@
         <v>101</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="AL42" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="AM42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN42" t="s" s="2">
         <v>321</v>
-      </c>
-      <c r="AM42" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN42" t="s" s="2">
-        <v>322</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6626,16 +6622,16 @@
         <v>90</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>325</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="N43" t="s" s="2">
         <v>326</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>327</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6664,11 +6660,11 @@
         <v>113</v>
       </c>
       <c r="Y43" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="Z43" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="Z43" t="s" s="2">
-        <v>329</v>
-      </c>
       <c r="AA43" t="s" s="2">
         <v>81</v>
       </c>
@@ -6685,7 +6681,7 @@
         <v>81</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -6700,28 +6696,28 @@
         <v>101</v>
       </c>
       <c r="AK43" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="AL43" t="s" s="2">
         <v>330</v>
       </c>
-      <c r="AL43" t="s" s="2">
+      <c r="AM43" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="AM43" t="s" s="2">
+      <c r="AN43" t="s" s="2">
         <v>332</v>
-      </c>
-      <c r="AN43" t="s" s="2">
-        <v>333</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -6740,16 +6736,16 @@
         <v>90</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="L44" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="L44" t="s" s="2">
-        <v>336</v>
-      </c>
       <c r="M44" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="N44" t="s" s="2">
         <v>326</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>327</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6799,7 +6795,7 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -6814,24 +6810,24 @@
         <v>101</v>
       </c>
       <c r="AK44" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="AL44" t="s" s="2">
         <v>330</v>
       </c>
-      <c r="AL44" t="s" s="2">
+      <c r="AM44" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="AM44" t="s" s="2">
+      <c r="AN44" t="s" s="2">
         <v>332</v>
-      </c>
-      <c r="AN44" t="s" s="2">
-        <v>333</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6854,13 +6850,13 @@
         <v>90</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>338</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>339</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6911,7 +6907,7 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -6929,7 +6925,7 @@
         <v>81</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>81</v>
@@ -6940,10 +6936,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6966,13 +6962,13 @@
         <v>81</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="L46" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="L46" t="s" s="2">
+      <c r="M46" t="s" s="2">
         <v>180</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>181</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7023,7 +7019,7 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -7041,7 +7037,7 @@
         <v>81</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>81</v>
@@ -7052,14 +7048,14 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7081,13 +7077,13 @@
         <v>134</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>184</v>
       </c>
-      <c r="M47" t="s" s="2">
-        <v>185</v>
-      </c>
       <c r="N47" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7137,7 +7133,7 @@
         <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -7155,7 +7151,7 @@
         <v>81</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>81</v>
@@ -7166,14 +7162,14 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7195,16 +7191,16 @@
         <v>134</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="M48" t="s" s="2">
-        <v>190</v>
-      </c>
       <c r="N48" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="O48" t="s" s="2">
         <v>150</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>151</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>81</v>
@@ -7253,7 +7249,7 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -7282,14 +7278,14 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7308,16 +7304,16 @@
         <v>90</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="L49" t="s" s="2">
         <v>346</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="M49" t="s" s="2">
         <v>347</v>
       </c>
-      <c r="M49" t="s" s="2">
-        <v>348</v>
-      </c>
       <c r="N49" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7367,7 +7363,7 @@
         <v>81</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>89</v>
@@ -7382,24 +7378,24 @@
         <v>101</v>
       </c>
       <c r="AK49" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="AL49" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="AL49" t="s" s="2">
+      <c r="AM49" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="AN49" t="s" s="2">
         <v>350</v>
-      </c>
-      <c r="AM49" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="AN49" t="s" s="2">
-        <v>351</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7422,13 +7418,13 @@
         <v>81</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>353</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>354</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7458,11 +7454,11 @@
         <v>113</v>
       </c>
       <c r="Y50" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="Z50" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="Z50" t="s" s="2">
-        <v>356</v>
-      </c>
       <c r="AA50" t="s" s="2">
         <v>81</v>
       </c>
@@ -7479,7 +7475,7 @@
         <v>81</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -7497,7 +7493,7 @@
         <v>81</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>81</v>
@@ -7508,10 +7504,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7534,13 +7530,13 @@
         <v>81</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="L51" t="s" s="2">
         <v>358</v>
       </c>
-      <c r="L51" t="s" s="2">
+      <c r="M51" t="s" s="2">
         <v>359</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>360</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7591,7 +7587,7 @@
         <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -7609,7 +7605,7 @@
         <v>81</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>81</v>
@@ -7620,10 +7616,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7646,16 +7642,16 @@
         <v>81</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="L52" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="L52" t="s" s="2">
+      <c r="M52" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="M52" t="s" s="2">
+      <c r="N52" t="s" s="2">
         <v>365</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>366</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -7705,7 +7701,7 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -7723,7 +7719,7 @@
         <v>81</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>81</v>
@@ -7734,10 +7730,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7760,16 +7756,16 @@
         <v>81</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>369</v>
       </c>
-      <c r="M53" t="s" s="2">
+      <c r="N53" t="s" s="2">
         <v>370</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>371</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -7819,7 +7815,7 @@
         <v>81</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -7837,7 +7833,7 @@
         <v>81</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>81</v>
@@ -7848,10 +7844,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7874,13 +7870,13 @@
         <v>81</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="L54" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="L54" t="s" s="2">
+      <c r="M54" t="s" s="2">
         <v>180</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>181</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -7931,7 +7927,7 @@
         <v>81</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -7949,7 +7945,7 @@
         <v>81</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>81</v>
@@ -7960,14 +7956,14 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -7989,13 +7985,13 @@
         <v>134</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>184</v>
       </c>
-      <c r="M55" t="s" s="2">
-        <v>185</v>
-      </c>
       <c r="N55" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8045,7 +8041,7 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8063,7 +8059,7 @@
         <v>81</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>81</v>
@@ -8074,14 +8070,14 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8103,16 +8099,16 @@
         <v>134</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="M56" t="s" s="2">
-        <v>190</v>
-      </c>
       <c r="N56" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="O56" t="s" s="2">
         <v>150</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>151</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>81</v>
@@ -8161,7 +8157,7 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8190,10 +8186,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8216,13 +8212,13 @@
         <v>81</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>377</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>378</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8273,7 +8269,7 @@
         <v>81</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -8291,21 +8287,21 @@
         <v>81</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8328,13 +8324,13 @@
         <v>81</v>
       </c>
       <c r="K58" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="L58" t="s" s="2">
         <v>381</v>
       </c>
-      <c r="L58" t="s" s="2">
+      <c r="M58" t="s" s="2">
         <v>382</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>383</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8385,7 +8381,7 @@
         <v>81</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -8403,7 +8399,7 @@
         <v>81</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>81</v>
@@ -8414,10 +8410,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8440,13 +8436,13 @@
         <v>81</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8476,11 +8472,11 @@
         <v>113</v>
       </c>
       <c r="Y59" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="Z59" t="s" s="2">
         <v>386</v>
       </c>
-      <c r="Z59" t="s" s="2">
-        <v>387</v>
-      </c>
       <c r="AA59" t="s" s="2">
         <v>81</v>
       </c>
@@ -8497,7 +8493,7 @@
         <v>81</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -8515,21 +8511,21 @@
         <v>81</v>
       </c>
       <c r="AL59" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="AM59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN59" t="s" s="2">
         <v>388</v>
-      </c>
-      <c r="AM59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN59" t="s" s="2">
-        <v>389</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8552,13 +8548,13 @@
         <v>81</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>391</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>392</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8585,14 +8581,14 @@
         <v>81</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="Y60" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="Z60" t="s" s="2">
         <v>393</v>
       </c>
-      <c r="Z60" t="s" s="2">
-        <v>394</v>
-      </c>
       <c r="AA60" t="s" s="2">
         <v>81</v>
       </c>
@@ -8609,7 +8605,7 @@
         <v>81</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -8627,21 +8623,21 @@
         <v>81</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8664,19 +8660,19 @@
         <v>81</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="M61" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="M61" t="s" s="2">
+      <c r="N61" t="s" s="2">
         <v>398</v>
       </c>
-      <c r="N61" t="s" s="2">
+      <c r="O61" t="s" s="2">
         <v>399</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>400</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>81</v>
@@ -8701,14 +8697,14 @@
         <v>81</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="Y61" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="Z61" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="Z61" t="s" s="2">
-        <v>402</v>
-      </c>
       <c r="AA61" t="s" s="2">
         <v>81</v>
       </c>
@@ -8725,7 +8721,7 @@
         <v>81</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -8743,21 +8739,21 @@
         <v>81</v>
       </c>
       <c r="AL61" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN61" t="s" s="2">
         <v>403</v>
-      </c>
-      <c r="AM61" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN61" t="s" s="2">
-        <v>404</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8780,13 +8776,13 @@
         <v>81</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="M62" t="s" s="2">
         <v>406</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>407</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -8816,11 +8812,11 @@
         <v>113</v>
       </c>
       <c r="Y62" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="Z62" t="s" s="2">
         <v>408</v>
       </c>
-      <c r="Z62" t="s" s="2">
-        <v>409</v>
-      </c>
       <c r="AA62" t="s" s="2">
         <v>81</v>
       </c>
@@ -8837,7 +8833,7 @@
         <v>81</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -8855,21 +8851,21 @@
         <v>81</v>
       </c>
       <c r="AL62" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="AM62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN62" t="s" s="2">
         <v>410</v>
-      </c>
-      <c r="AM62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN62" t="s" s="2">
-        <v>411</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8892,13 +8888,13 @@
         <v>81</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>413</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>414</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -8928,11 +8924,11 @@
         <v>113</v>
       </c>
       <c r="Y63" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="Z63" t="s" s="2">
         <v>415</v>
       </c>
-      <c r="Z63" t="s" s="2">
-        <v>416</v>
-      </c>
       <c r="AA63" t="s" s="2">
         <v>81</v>
       </c>
@@ -8949,7 +8945,7 @@
         <v>81</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -8967,21 +8963,21 @@
         <v>81</v>
       </c>
       <c r="AL63" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="AM63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN63" t="s" s="2">
         <v>417</v>
-      </c>
-      <c r="AM63" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN63" t="s" s="2">
-        <v>418</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9004,13 +9000,13 @@
         <v>81</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>420</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>421</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9061,7 +9057,7 @@
         <v>81</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -9079,21 +9075,21 @@
         <v>81</v>
       </c>
       <c r="AL64" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN64" t="s" s="2">
         <v>422</v>
-      </c>
-      <c r="AM64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN64" t="s" s="2">
-        <v>423</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9116,13 +9112,13 @@
         <v>81</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="L65" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="M65" t="s" s="2">
         <v>425</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>426</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9149,13 +9145,13 @@
         <v>81</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>81</v>
@@ -9173,7 +9169,7 @@
         <v>81</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -9191,21 +9187,21 @@
         <v>81</v>
       </c>
       <c r="AL65" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN65" t="s" s="2">
         <v>428</v>
-      </c>
-      <c r="AM65" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN65" t="s" s="2">
-        <v>429</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9228,16 +9224,16 @@
         <v>81</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="M66" t="s" s="2">
         <v>431</v>
       </c>
-      <c r="M66" t="s" s="2">
+      <c r="N66" t="s" s="2">
         <v>432</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>433</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -9287,7 +9283,7 @@
         <v>81</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -9305,7 +9301,7 @@
         <v>81</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>81</v>
@@ -9316,10 +9312,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9342,13 +9338,13 @@
         <v>81</v>
       </c>
       <c r="K67" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="L67" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="L67" t="s" s="2">
+      <c r="M67" t="s" s="2">
         <v>180</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>181</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9399,7 +9395,7 @@
         <v>81</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -9417,7 +9413,7 @@
         <v>81</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>81</v>
@@ -9428,14 +9424,14 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -9457,13 +9453,13 @@
         <v>134</v>
       </c>
       <c r="L68" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="M68" t="s" s="2">
         <v>184</v>
       </c>
-      <c r="M68" t="s" s="2">
-        <v>185</v>
-      </c>
       <c r="N68" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -9513,7 +9509,7 @@
         <v>81</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -9531,7 +9527,7 @@
         <v>81</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>81</v>
@@ -9542,14 +9538,14 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -9571,16 +9567,16 @@
         <v>134</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="M69" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="M69" t="s" s="2">
-        <v>190</v>
-      </c>
       <c r="N69" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="O69" t="s" s="2">
         <v>150</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>151</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>81</v>
@@ -9629,7 +9625,7 @@
         <v>81</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -9658,10 +9654,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9684,13 +9680,13 @@
         <v>81</v>
       </c>
       <c r="K70" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="L70" t="s" s="2">
         <v>439</v>
       </c>
-      <c r="L70" t="s" s="2">
+      <c r="M70" t="s" s="2">
         <v>440</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>441</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -9741,7 +9737,7 @@
         <v>81</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>89</v>
@@ -9756,24 +9752,24 @@
         <v>101</v>
       </c>
       <c r="AK70" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="AM70" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="AL70" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="AM70" t="s" s="2">
+      <c r="AN70" t="s" s="2">
         <v>443</v>
-      </c>
-      <c r="AN70" t="s" s="2">
-        <v>444</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9799,13 +9795,13 @@
         <v>109</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="M71" t="s" s="2">
         <v>446</v>
       </c>
-      <c r="M71" t="s" s="2">
+      <c r="N71" t="s" s="2">
         <v>447</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>448</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -9831,14 +9827,14 @@
         <v>81</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="Y71" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="Z71" t="s" s="2">
         <v>449</v>
       </c>
-      <c r="Z71" t="s" s="2">
-        <v>450</v>
-      </c>
       <c r="AA71" t="s" s="2">
         <v>81</v>
       </c>
@@ -9855,7 +9851,7 @@
         <v>81</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -9873,7 +9869,7 @@
         <v>81</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>81</v>
@@ -9884,10 +9880,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9910,16 +9906,16 @@
         <v>81</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="L72" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="M72" t="s" s="2">
         <v>453</v>
       </c>
-      <c r="M72" t="s" s="2">
+      <c r="N72" t="s" s="2">
         <v>454</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>455</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -9945,14 +9941,14 @@
         <v>81</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="Y72" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="Z72" t="s" s="2">
         <v>456</v>
       </c>
-      <c r="Z72" t="s" s="2">
-        <v>457</v>
-      </c>
       <c r="AA72" t="s" s="2">
         <v>81</v>
       </c>
@@ -9969,7 +9965,7 @@
         <v>81</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -9998,10 +9994,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10024,13 +10020,13 @@
         <v>81</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10081,7 +10077,7 @@
         <v>81</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
@@ -10099,7 +10095,7 @@
         <v>81</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>81</v>
@@ -10110,10 +10106,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10136,13 +10132,13 @@
         <v>81</v>
       </c>
       <c r="K74" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="L74" t="s" s="2">
         <v>461</v>
       </c>
-      <c r="L74" t="s" s="2">
+      <c r="M74" t="s" s="2">
         <v>462</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>463</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -10193,7 +10189,7 @@
         <v>81</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -10208,24 +10204,24 @@
         <v>101</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="AL74" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN74" t="s" s="2">
         <v>464</v>
-      </c>
-      <c r="AM74" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN74" t="s" s="2">
-        <v>465</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10248,16 +10244,16 @@
         <v>81</v>
       </c>
       <c r="K75" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="L75" t="s" s="2">
         <v>467</v>
       </c>
-      <c r="L75" t="s" s="2">
+      <c r="M75" t="s" s="2">
         <v>468</v>
       </c>
-      <c r="M75" t="s" s="2">
+      <c r="N75" t="s" s="2">
         <v>469</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>470</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -10307,7 +10303,7 @@
         <v>81</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
@@ -10322,10 +10318,10 @@
         <v>101</v>
       </c>
       <c r="AK75" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="AL75" t="s" s="2">
         <v>471</v>
-      </c>
-      <c r="AL75" t="s" s="2">
-        <v>472</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>81</v>

--- a/jpcore-r4/develop-kohetest/StructureDefinition-jp-encounter.xlsx
+++ b/jpcore-r4/develop-kohetest/StructureDefinition-jp-encounter.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2716" uniqueCount="472">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2716" uniqueCount="474">
   <si>
     <t>Property</t>
   </si>
@@ -460,11 +460,19 @@
     <t>associatedEncounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {encounter-associatedEncounter|latest}
+    <t xml:space="preserve">Extension {encounter-associatedEncounter|4.0.1}
 </t>
   </si>
   <si>
     <t>関連するEncounter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>Encounter.modifierExtension</t>
@@ -2946,10 +2954,10 @@
         <v>80</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>81</v>
+        <v>145</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>81</v>
@@ -2966,14 +2974,14 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
@@ -2995,16 +3003,16 @@
         <v>134</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="O11" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>81</v>
@@ -3053,7 +3061,7 @@
         <v>81</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>79</v>
@@ -3082,10 +3090,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3108,13 +3116,13 @@
         <v>90</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -3165,7 +3173,7 @@
         <v>81</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>79</v>
@@ -3180,24 +3188,24 @@
         <v>101</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3223,13 +3231,13 @@
         <v>109</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3255,13 +3263,13 @@
         <v>81</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>81</v>
@@ -3279,7 +3287,7 @@
         <v>81</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>89</v>
@@ -3294,24 +3302,24 @@
         <v>101</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3334,16 +3342,16 @@
         <v>81</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3393,7 +3401,7 @@
         <v>81</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>79</v>
@@ -3411,7 +3419,7 @@
         <v>81</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="AM14" t="s" s="2">
         <v>81</v>
@@ -3422,10 +3430,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3448,13 +3456,13 @@
         <v>81</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -3505,7 +3513,7 @@
         <v>81</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>79</v>
@@ -3523,7 +3531,7 @@
         <v>81</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>81</v>
@@ -3534,14 +3542,14 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3563,13 +3571,13 @@
         <v>134</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3619,7 +3627,7 @@
         <v>81</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
@@ -3637,7 +3645,7 @@
         <v>81</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>81</v>
@@ -3648,14 +3656,14 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3677,16 +3685,16 @@
         <v>134</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>81</v>
@@ -3735,7 +3743,7 @@
         <v>81</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -3764,10 +3772,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3793,13 +3801,13 @@
         <v>109</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3825,13 +3833,13 @@
         <v>81</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>81</v>
@@ -3849,7 +3857,7 @@
         <v>81</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>89</v>
@@ -3867,7 +3875,7 @@
         <v>81</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>81</v>
@@ -3878,10 +3886,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3904,16 +3912,16 @@
         <v>81</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3963,7 +3971,7 @@
         <v>81</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>89</v>
@@ -3981,7 +3989,7 @@
         <v>81</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>81</v>
@@ -3992,10 +4000,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4018,16 +4026,16 @@
         <v>90</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4053,13 +4061,13 @@
         <v>81</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>81</v>
@@ -4077,7 +4085,7 @@
         <v>81</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>89</v>
@@ -4095,21 +4103,21 @@
         <v>81</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4132,13 +4140,13 @@
         <v>81</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4189,7 +4197,7 @@
         <v>81</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -4207,7 +4215,7 @@
         <v>81</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>81</v>
@@ -4218,10 +4226,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4244,13 +4252,13 @@
         <v>81</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4301,7 +4309,7 @@
         <v>81</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -4319,7 +4327,7 @@
         <v>81</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>81</v>
@@ -4330,14 +4338,14 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -4359,13 +4367,13 @@
         <v>134</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4415,7 +4423,7 @@
         <v>81</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -4433,7 +4441,7 @@
         <v>81</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>81</v>
@@ -4444,14 +4452,14 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4473,16 +4481,16 @@
         <v>134</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>81</v>
@@ -4531,7 +4539,7 @@
         <v>81</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -4560,10 +4568,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4586,16 +4594,16 @@
         <v>81</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4621,13 +4629,13 @@
         <v>81</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>81</v>
@@ -4645,7 +4653,7 @@
         <v>81</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>89</v>
@@ -4663,7 +4671,7 @@
         <v>81</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>81</v>
@@ -4674,10 +4682,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4700,16 +4708,16 @@
         <v>81</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4759,7 +4767,7 @@
         <v>81</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>89</v>
@@ -4777,7 +4785,7 @@
         <v>81</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>81</v>
@@ -4788,10 +4796,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4814,16 +4822,16 @@
         <v>90</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -4849,13 +4857,13 @@
         <v>81</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>81</v>
@@ -4873,7 +4881,7 @@
         <v>81</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -4888,24 +4896,24 @@
         <v>101</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4928,13 +4936,13 @@
         <v>90</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4961,13 +4969,13 @@
         <v>81</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>81</v>
@@ -4985,7 +4993,7 @@
         <v>81</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -5000,24 +5008,24 @@
         <v>101</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5040,13 +5048,13 @@
         <v>81</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5073,31 +5081,31 @@
         <v>81</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Y29" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="Z29" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="AA29" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB29" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC29" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD29" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE29" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF29" t="s" s="2">
         <v>242</v>
-      </c>
-      <c r="Z29" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="AA29" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB29" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC29" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD29" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE29" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF29" t="s" s="2">
-        <v>240</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -5115,25 +5123,25 @@
         <v>81</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -5152,16 +5160,16 @@
         <v>90</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5211,7 +5219,7 @@
         <v>81</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -5226,24 +5234,24 @@
         <v>101</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5266,13 +5274,13 @@
         <v>90</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5323,7 +5331,7 @@
         <v>81</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -5338,28 +5346,28 @@
         <v>101</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5378,13 +5386,13 @@
         <v>81</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5435,7 +5443,7 @@
         <v>81</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -5450,10 +5458,10 @@
         <v>101</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>81</v>
@@ -5464,10 +5472,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5490,13 +5498,13 @@
         <v>90</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5547,7 +5555,7 @@
         <v>81</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -5562,24 +5570,24 @@
         <v>101</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5602,13 +5610,13 @@
         <v>81</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5659,7 +5667,7 @@
         <v>81</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -5677,7 +5685,7 @@
         <v>81</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>81</v>
@@ -5688,14 +5696,14 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -5717,13 +5725,13 @@
         <v>134</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5773,7 +5781,7 @@
         <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -5791,7 +5799,7 @@
         <v>81</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>81</v>
@@ -5802,14 +5810,14 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -5831,16 +5839,16 @@
         <v>134</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>81</v>
@@ -5889,7 +5897,7 @@
         <v>81</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -5918,10 +5926,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5944,16 +5952,16 @@
         <v>90</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -5979,31 +5987,31 @@
         <v>81</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Y37" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="Z37" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="AA37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF37" t="s" s="2">
         <v>282</v>
-      </c>
-      <c r="Z37" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="AA37" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB37" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC37" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD37" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE37" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF37" t="s" s="2">
-        <v>280</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -6018,24 +6026,24 @@
         <v>101</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6058,13 +6066,13 @@
         <v>81</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6115,7 +6123,7 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -6133,21 +6141,21 @@
         <v>81</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6170,13 +6178,13 @@
         <v>90</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6227,7 +6235,7 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -6242,24 +6250,24 @@
         <v>101</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6282,13 +6290,13 @@
         <v>90</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6339,7 +6347,7 @@
         <v>81</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -6354,24 +6362,24 @@
         <v>101</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6394,16 +6402,16 @@
         <v>81</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6453,7 +6461,7 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -6468,24 +6476,24 @@
         <v>101</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6508,16 +6516,16 @@
         <v>81</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6567,7 +6575,7 @@
         <v>81</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -6582,28 +6590,28 @@
         <v>101</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6622,16 +6630,16 @@
         <v>90</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6660,10 +6668,10 @@
         <v>113</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>81</v>
@@ -6681,7 +6689,7 @@
         <v>81</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -6696,28 +6704,28 @@
         <v>101</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -6736,16 +6744,16 @@
         <v>90</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6795,7 +6803,7 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -6810,24 +6818,24 @@
         <v>101</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6850,13 +6858,13 @@
         <v>90</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6907,7 +6915,7 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -6925,7 +6933,7 @@
         <v>81</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>81</v>
@@ -6936,10 +6944,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6962,13 +6970,13 @@
         <v>81</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7019,7 +7027,7 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -7037,7 +7045,7 @@
         <v>81</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>81</v>
@@ -7048,14 +7056,14 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7077,13 +7085,13 @@
         <v>134</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7133,7 +7141,7 @@
         <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -7151,7 +7159,7 @@
         <v>81</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>81</v>
@@ -7162,14 +7170,14 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7191,16 +7199,16 @@
         <v>134</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>81</v>
@@ -7249,7 +7257,7 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -7278,14 +7286,14 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7304,16 +7312,16 @@
         <v>90</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7363,7 +7371,7 @@
         <v>81</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>89</v>
@@ -7378,24 +7386,24 @@
         <v>101</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7418,13 +7426,13 @@
         <v>81</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7454,10 +7462,10 @@
         <v>113</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>81</v>
@@ -7475,7 +7483,7 @@
         <v>81</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -7493,7 +7501,7 @@
         <v>81</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>81</v>
@@ -7504,10 +7512,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7530,13 +7538,13 @@
         <v>81</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7587,7 +7595,7 @@
         <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -7605,7 +7613,7 @@
         <v>81</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>81</v>
@@ -7616,10 +7624,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7642,16 +7650,16 @@
         <v>81</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -7701,7 +7709,7 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -7719,7 +7727,7 @@
         <v>81</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>81</v>
@@ -7730,10 +7738,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7756,16 +7764,16 @@
         <v>81</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -7815,7 +7823,7 @@
         <v>81</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -7833,7 +7841,7 @@
         <v>81</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>81</v>
@@ -7844,10 +7852,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7870,13 +7878,13 @@
         <v>81</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -7927,7 +7935,7 @@
         <v>81</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -7945,7 +7953,7 @@
         <v>81</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>81</v>
@@ -7956,14 +7964,14 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -7985,13 +7993,13 @@
         <v>134</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8041,7 +8049,7 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8059,7 +8067,7 @@
         <v>81</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>81</v>
@@ -8070,14 +8078,14 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8099,16 +8107,16 @@
         <v>134</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>81</v>
@@ -8157,7 +8165,7 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8186,10 +8194,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8212,13 +8220,13 @@
         <v>81</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8269,7 +8277,7 @@
         <v>81</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -8287,21 +8295,21 @@
         <v>81</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8324,13 +8332,13 @@
         <v>81</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8381,7 +8389,7 @@
         <v>81</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -8399,7 +8407,7 @@
         <v>81</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>81</v>
@@ -8410,10 +8418,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8436,13 +8444,13 @@
         <v>81</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8472,28 +8480,28 @@
         <v>113</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="Z59" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF59" t="s" s="2">
         <v>386</v>
-      </c>
-      <c r="AA59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF59" t="s" s="2">
-        <v>384</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -8511,21 +8519,21 @@
         <v>81</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8548,13 +8556,13 @@
         <v>81</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8581,13 +8589,13 @@
         <v>81</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>81</v>
@@ -8605,7 +8613,7 @@
         <v>81</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -8623,21 +8631,21 @@
         <v>81</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8660,19 +8668,19 @@
         <v>81</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>81</v>
@@ -8697,13 +8705,13 @@
         <v>81</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>81</v>
@@ -8721,7 +8729,7 @@
         <v>81</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -8739,21 +8747,21 @@
         <v>81</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8776,13 +8784,13 @@
         <v>81</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -8812,10 +8820,10 @@
         <v>113</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>81</v>
@@ -8833,7 +8841,7 @@
         <v>81</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -8851,21 +8859,21 @@
         <v>81</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8888,13 +8896,13 @@
         <v>81</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -8924,10 +8932,10 @@
         <v>113</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>81</v>
@@ -8945,7 +8953,7 @@
         <v>81</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -8963,21 +8971,21 @@
         <v>81</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9000,13 +9008,13 @@
         <v>81</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9057,7 +9065,7 @@
         <v>81</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -9075,21 +9083,21 @@
         <v>81</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9112,13 +9120,13 @@
         <v>81</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9145,13 +9153,13 @@
         <v>81</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>81</v>
@@ -9169,7 +9177,7 @@
         <v>81</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -9187,21 +9195,21 @@
         <v>81</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9224,16 +9232,16 @@
         <v>81</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -9283,7 +9291,7 @@
         <v>81</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -9301,7 +9309,7 @@
         <v>81</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>81</v>
@@ -9312,10 +9320,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9338,13 +9346,13 @@
         <v>81</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9395,7 +9403,7 @@
         <v>81</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -9413,7 +9421,7 @@
         <v>81</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>81</v>
@@ -9424,14 +9432,14 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -9453,13 +9461,13 @@
         <v>134</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -9509,7 +9517,7 @@
         <v>81</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -9527,7 +9535,7 @@
         <v>81</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>81</v>
@@ -9538,14 +9546,14 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -9567,16 +9575,16 @@
         <v>134</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>81</v>
@@ -9625,7 +9633,7 @@
         <v>81</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -9654,10 +9662,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9680,13 +9688,13 @@
         <v>81</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -9737,7 +9745,7 @@
         <v>81</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>89</v>
@@ -9752,24 +9760,24 @@
         <v>101</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9795,13 +9803,13 @@
         <v>109</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -9827,13 +9835,13 @@
         <v>81</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>81</v>
@@ -9851,7 +9859,7 @@
         <v>81</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -9869,7 +9877,7 @@
         <v>81</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>81</v>
@@ -9880,10 +9888,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9906,16 +9914,16 @@
         <v>81</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -9941,13 +9949,13 @@
         <v>81</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>81</v>
@@ -9965,7 +9973,7 @@
         <v>81</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -9994,10 +10002,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10020,13 +10028,13 @@
         <v>81</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10077,7 +10085,7 @@
         <v>81</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
@@ -10095,7 +10103,7 @@
         <v>81</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>81</v>
@@ -10106,10 +10114,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10132,13 +10140,13 @@
         <v>81</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -10189,7 +10197,7 @@
         <v>81</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -10204,24 +10212,24 @@
         <v>101</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10244,16 +10252,16 @@
         <v>81</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -10303,7 +10311,7 @@
         <v>81</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
@@ -10318,10 +10326,10 @@
         <v>101</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>81</v>

--- a/jpcore-r4/develop-kohetest/StructureDefinition-jp-encounter.xlsx
+++ b/jpcore-r4/develop-kohetest/StructureDefinition-jp-encounter.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2716" uniqueCount="474">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2716" uniqueCount="473">
   <si>
     <t>Property</t>
   </si>
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Encounter</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Encounter|4.0.1</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -369,7 +369,7 @@
     <t>人間の言語。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -460,19 +460,15 @@
     <t>associatedEncounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {encounter-associatedEncounter|4.0.1}
+    <t xml:space="preserve">Extension {encounter-associatedEncounter|5.2.0}
 </t>
   </si>
   <si>
     <t>関連するEncounter</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>Encounter.modifierExtension</t>
@@ -667,7 +663,7 @@
     <t>受療行動の分類。</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/ValueSet/v3-ActEncounterCode</t>
+    <t>http://terminology.hl7.org/ValueSet/v3-ActEncounterCode|3.0.0</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=SUBJ].source[classCode=LIST].code</t>
@@ -741,7 +737,7 @@
     <t>受療行動のタイプ。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/encounter-type</t>
+    <t>http://hl7.org/fhir/ValueSet/encounter-type|4.0.1</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -765,7 +761,7 @@
     <t>提供されるサービスの広範な分類。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/service-type</t>
+    <t>http://hl7.org/fhir/ValueSet/service-type|4.0.1</t>
   </si>
   <si>
     <t>PV1-10</t>
@@ -780,7 +776,7 @@
     <t>受療行動の緊急性を示します。</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/ValueSet/v3-ActPriority</t>
+    <t>http://terminology.hl7.org/ValueSet/v3-ActPriority|3.0.0</t>
   </si>
   <si>
     <t>.priorityCode</t>
@@ -799,7 +795,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|Group)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|1.3.0-dev|Group|4.0.1)
 </t>
   </si>
   <si>
@@ -827,7 +823,7 @@
     <t>Encounter.episodeOfCare</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(EpisodeOfCare)
+    <t xml:space="preserve">Reference(EpisodeOfCare|4.0.1)
 </t>
   </si>
   <si>
@@ -853,7 +849,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(ServiceRequest)
+    <t xml:space="preserve">Reference(ServiceRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -908,7 +904,7 @@
     <t>参加者タイプは、個人がどのようにエンカウントに参加するかを示します。それには、非開業者の参加者が含まれ、開業者にとってはこのエンカウントの文脈でアクションタイプを説明することが含まれます（例：入院医師、診療医師、翻訳者、相談医師）。これは、雇用、教育、免許などの用語から派生した機能的な役割である開業者の役割とは異なります。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/encounter-participant-type</t>
+    <t>http://hl7.org/fhir/ValueSet/encounter-participant-type|4.0.1</t>
   </si>
   <si>
     <t>Event.performer.function</t>
@@ -938,7 +934,7 @@
     <t>Encounter.participant.individual</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole|RelatedPerson)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole|1.3.0-dev|RelatedPerson|4.0.1)
 </t>
   </si>
   <si>
@@ -963,7 +959,7 @@
     <t>Encounter.appointment</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Appointment)
+    <t xml:space="preserve">Reference(Appointment|4.0.1)
 </t>
   </si>
   <si>
@@ -1044,7 +1040,7 @@
     <t>受療行動が起こる理由。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/encounter-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/encounter-reason|4.0.1</t>
   </si>
   <si>
     <t>Event.reasonCode</t>
@@ -1062,7 +1058,7 @@
     <t>Encounter.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Condition|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Condition_Diagnosis|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Procedure|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Common|ImmunizationRecommendation)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Condition|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Condition_Diagnosis|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Procedure|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Common|1.3.0-dev|ImmunizationRecommendation|4.0.1)
 </t>
   </si>
   <si>
@@ -1097,7 +1093,7 @@
 discharge diagnosisindication</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Condition|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Condition_Diagnosis|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Procedure)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Condition|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Condition_Diagnosis|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Procedure|1.3.0-dev)
 </t>
   </si>
   <si>
@@ -1128,7 +1124,7 @@
     <t>この状態が表す診断のタイプ。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/diagnosis-role</t>
+    <t>http://hl7.org/fhir/ValueSet/diagnosis-role|4.0.1</t>
   </si>
   <si>
     <t>Encounter.diagnosis.rank</t>
@@ -1150,7 +1146,7 @@
     <t>Encounter.account</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Account)
+    <t xml:space="preserve">Reference(Account|4.0.1)
 </t>
   </si>
   <si>
@@ -1206,7 +1202,7 @@
     <t>Encounter.hospitalization.origin</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Location|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Location|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization|1.3.0-dev)
 </t>
   </si>
   <si>
@@ -1225,7 +1221,7 @@
     <t>患者がどこから入院したのか（医師の紹介、転院）</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/encounter-admit-source</t>
+    <t>http://hl7.org/fhir/ValueSet/encounter-admit-source|4.0.1</t>
   </si>
   <si>
     <t>.admissionReferralSourceCode</t>
@@ -1246,7 +1242,7 @@
     <t>この入院の再入院の理由。</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/ValueSet/v2-0092</t>
+    <t>http://terminology.hl7.org/ValueSet/v2-0092|2.0.0</t>
   </si>
   <si>
     <t>PV1-13</t>
@@ -1270,7 +1266,7 @@
     <t>食品の好みを考慮して、医療、文化、倫理的観点から、提供要件に対応することができます。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/encounter-diet</t>
+    <t>http://hl7.org/fhir/ValueSet/encounter-diet|4.0.1</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode=COMP].target[classCode=SBADM, moodCode=EVN, code="diet"]</t>
@@ -1291,7 +1287,7 @@
     <t>特別なおもてなし。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/encounter-special-courtesy</t>
+    <t>http://hl7.org/fhir/ValueSet/encounter-special-courtesy|4.0.1</t>
   </si>
   <si>
     <t>.specialCourtesiesCode</t>
@@ -1312,7 +1308,7 @@
     <t>特別な手配。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/encounter-special-arrangements</t>
+    <t>http://hl7.org/fhir/ValueSet/encounter-special-arrangements|4.0.1</t>
   </si>
   <si>
     <t>.specialArrangementCode</t>
@@ -1345,7 +1341,7 @@
     <t>退院後の場所のカテゴリーまたは種類。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/encounter-discharge-disposition</t>
+    <t>http://hl7.org/fhir/ValueSet/encounter-discharge-disposition|4.0.1</t>
   </si>
   <si>
     <t>.dischargeDispositionCode</t>
@@ -1381,7 +1377,7 @@
     <t>Encounter.location.location</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Location)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Location|1.3.0-dev)
 </t>
   </si>
   <si>
@@ -1437,7 +1433,7 @@
     <t>場所の実体形態。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/location-physical-type</t>
+    <t>http://hl7.org/fhir/ValueSet/location-physical-type|4.0.1</t>
   </si>
   <si>
     <t>Encounter.location.period</t>
@@ -1449,7 +1445,7 @@
     <t>Encounter.serviceProvider</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization|1.3.0-dev)
 </t>
   </si>
   <si>
@@ -1468,7 +1464,7 @@
     <t>Encounter.partOf</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Encounter)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Encounter|1.3.0-dev)
 </t>
   </si>
   <si>
@@ -1801,7 +1797,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="230.390625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1816,7 +1812,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="40.51171875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="48.2265625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="52.75390625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
@@ -2954,10 +2950,10 @@
         <v>80</v>
       </c>
       <c r="AI10" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ10" t="s" s="2">
         <v>145</v>
-      </c>
-      <c r="AJ10" t="s" s="2">
-        <v>146</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>81</v>
@@ -2974,14 +2970,14 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
@@ -3003,16 +2999,16 @@
         <v>134</v>
       </c>
       <c r="L11" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="M11" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="M11" t="s" s="2">
+      <c r="N11" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="N11" t="s" s="2">
+      <c r="O11" t="s" s="2">
         <v>151</v>
-      </c>
-      <c r="O11" t="s" s="2">
-        <v>152</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>81</v>
@@ -3061,7 +3057,7 @@
         <v>81</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>79</v>
@@ -3090,10 +3086,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3116,13 +3112,13 @@
         <v>90</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="L12" t="s" s="2">
         <v>155</v>
       </c>
-      <c r="L12" t="s" s="2">
+      <c r="M12" t="s" s="2">
         <v>156</v>
-      </c>
-      <c r="M12" t="s" s="2">
-        <v>157</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -3173,7 +3169,7 @@
         <v>81</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>79</v>
@@ -3188,24 +3184,24 @@
         <v>101</v>
       </c>
       <c r="AK12" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="AL12" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="AL12" t="s" s="2">
+      <c r="AM12" t="s" s="2">
         <v>159</v>
       </c>
-      <c r="AM12" t="s" s="2">
+      <c r="AN12" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="AN12" t="s" s="2">
-        <v>161</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3231,13 +3227,13 @@
         <v>109</v>
       </c>
       <c r="L13" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="M13" t="s" s="2">
         <v>163</v>
       </c>
-      <c r="M13" t="s" s="2">
+      <c r="N13" t="s" s="2">
         <v>164</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>165</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3263,14 +3259,14 @@
         <v>81</v>
       </c>
       <c r="X13" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="Y13" t="s" s="2">
         <v>166</v>
       </c>
-      <c r="Y13" t="s" s="2">
+      <c r="Z13" t="s" s="2">
         <v>167</v>
       </c>
-      <c r="Z13" t="s" s="2">
-        <v>168</v>
-      </c>
       <c r="AA13" t="s" s="2">
         <v>81</v>
       </c>
@@ -3287,7 +3283,7 @@
         <v>81</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>89</v>
@@ -3302,24 +3298,24 @@
         <v>101</v>
       </c>
       <c r="AK13" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="AL13" t="s" s="2">
         <v>169</v>
       </c>
-      <c r="AL13" t="s" s="2">
+      <c r="AM13" t="s" s="2">
         <v>170</v>
       </c>
-      <c r="AM13" t="s" s="2">
+      <c r="AN13" t="s" s="2">
         <v>171</v>
-      </c>
-      <c r="AN13" t="s" s="2">
-        <v>172</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3342,16 +3338,16 @@
         <v>81</v>
       </c>
       <c r="K14" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="L14" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="L14" t="s" s="2">
+      <c r="M14" t="s" s="2">
         <v>175</v>
       </c>
-      <c r="M14" t="s" s="2">
+      <c r="N14" t="s" s="2">
         <v>176</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>177</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3401,7 +3397,7 @@
         <v>81</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>79</v>
@@ -3419,7 +3415,7 @@
         <v>81</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AM14" t="s" s="2">
         <v>81</v>
@@ -3430,10 +3426,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3456,13 +3452,13 @@
         <v>81</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="L15" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="L15" t="s" s="2">
+      <c r="M15" t="s" s="2">
         <v>181</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>182</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -3513,7 +3509,7 @@
         <v>81</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>79</v>
@@ -3531,7 +3527,7 @@
         <v>81</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>81</v>
@@ -3542,14 +3538,14 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3571,13 +3567,13 @@
         <v>134</v>
       </c>
       <c r="L16" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="M16" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="M16" t="s" s="2">
-        <v>186</v>
-      </c>
       <c r="N16" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3627,7 +3623,7 @@
         <v>81</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
@@ -3645,7 +3641,7 @@
         <v>81</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>81</v>
@@ -3656,14 +3652,14 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3685,16 +3681,16 @@
         <v>134</v>
       </c>
       <c r="L17" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>190</v>
       </c>
-      <c r="M17" t="s" s="2">
-        <v>191</v>
-      </c>
       <c r="N17" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="O17" t="s" s="2">
         <v>151</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>152</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>81</v>
@@ -3743,7 +3739,7 @@
         <v>81</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -3772,10 +3768,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3801,13 +3797,13 @@
         <v>109</v>
       </c>
       <c r="L18" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="M18" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="N18" t="s" s="2">
         <v>194</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>195</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3833,14 +3829,14 @@
         <v>81</v>
       </c>
       <c r="X18" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="Y18" t="s" s="2">
         <v>166</v>
       </c>
-      <c r="Y18" t="s" s="2">
+      <c r="Z18" t="s" s="2">
         <v>167</v>
       </c>
-      <c r="Z18" t="s" s="2">
-        <v>168</v>
-      </c>
       <c r="AA18" t="s" s="2">
         <v>81</v>
       </c>
@@ -3857,7 +3853,7 @@
         <v>81</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>89</v>
@@ -3875,7 +3871,7 @@
         <v>81</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>81</v>
@@ -3886,10 +3882,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3912,16 +3908,16 @@
         <v>81</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="M19" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="M19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>199</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>200</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3971,7 +3967,7 @@
         <v>81</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>89</v>
@@ -3989,7 +3985,7 @@
         <v>81</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>81</v>
@@ -4000,10 +3996,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4026,16 +4022,16 @@
         <v>90</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>202</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="M20" t="s" s="2">
         <v>203</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>204</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>205</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4061,14 +4057,14 @@
         <v>81</v>
       </c>
       <c r="X20" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="Y20" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="Y20" t="s" s="2">
+      <c r="Z20" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="Z20" t="s" s="2">
-        <v>208</v>
-      </c>
       <c r="AA20" t="s" s="2">
         <v>81</v>
       </c>
@@ -4085,7 +4081,7 @@
         <v>81</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>89</v>
@@ -4103,21 +4099,21 @@
         <v>81</v>
       </c>
       <c r="AL20" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="AM20" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="AM20" t="s" s="2">
+      <c r="AN20" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="AN20" t="s" s="2">
-        <v>211</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4140,13 +4136,13 @@
         <v>81</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L21" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="M21" t="s" s="2">
         <v>213</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>214</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4197,7 +4193,7 @@
         <v>81</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -4215,7 +4211,7 @@
         <v>81</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>81</v>
@@ -4226,10 +4222,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4252,13 +4248,13 @@
         <v>81</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="L22" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="L22" t="s" s="2">
+      <c r="M22" t="s" s="2">
         <v>181</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>182</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4309,7 +4305,7 @@
         <v>81</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -4327,7 +4323,7 @@
         <v>81</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>81</v>
@@ -4338,14 +4334,14 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -4367,13 +4363,13 @@
         <v>134</v>
       </c>
       <c r="L23" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="M23" t="s" s="2">
-        <v>186</v>
-      </c>
       <c r="N23" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4423,7 +4419,7 @@
         <v>81</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -4441,7 +4437,7 @@
         <v>81</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>81</v>
@@ -4452,14 +4448,14 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4481,16 +4477,16 @@
         <v>134</v>
       </c>
       <c r="L24" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>190</v>
       </c>
-      <c r="M24" t="s" s="2">
-        <v>191</v>
-      </c>
       <c r="N24" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="O24" t="s" s="2">
         <v>151</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>152</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>81</v>
@@ -4539,7 +4535,7 @@
         <v>81</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -4568,10 +4564,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4594,16 +4590,16 @@
         <v>81</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>220</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>221</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4629,14 +4625,14 @@
         <v>81</v>
       </c>
       <c r="X25" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="Y25" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="Y25" t="s" s="2">
+      <c r="Z25" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="Z25" t="s" s="2">
-        <v>208</v>
-      </c>
       <c r="AA25" t="s" s="2">
         <v>81</v>
       </c>
@@ -4653,7 +4649,7 @@
         <v>81</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>89</v>
@@ -4671,7 +4667,7 @@
         <v>81</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>81</v>
@@ -4682,10 +4678,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4708,16 +4704,16 @@
         <v>81</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>223</v>
       </c>
-      <c r="M26" t="s" s="2">
-        <v>224</v>
-      </c>
       <c r="N26" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4767,7 +4763,7 @@
         <v>81</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>89</v>
@@ -4785,7 +4781,7 @@
         <v>81</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>81</v>
@@ -4796,10 +4792,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4822,16 +4818,16 @@
         <v>90</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="L27" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="M27" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>228</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>229</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -4857,14 +4853,14 @@
         <v>81</v>
       </c>
       <c r="X27" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="Y27" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="Y27" t="s" s="2">
+      <c r="Z27" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="Z27" t="s" s="2">
-        <v>232</v>
-      </c>
       <c r="AA27" t="s" s="2">
         <v>81</v>
       </c>
@@ -4881,7 +4877,7 @@
         <v>81</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -4896,24 +4892,24 @@
         <v>101</v>
       </c>
       <c r="AK27" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="AL27" t="s" s="2">
         <v>233</v>
       </c>
-      <c r="AL27" t="s" s="2">
+      <c r="AM27" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="AN27" t="s" s="2">
         <v>234</v>
-      </c>
-      <c r="AM27" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>235</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4936,13 +4932,13 @@
         <v>90</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>237</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>238</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4969,14 +4965,14 @@
         <v>81</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="Y28" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="Z28" t="s" s="2">
         <v>239</v>
       </c>
-      <c r="Z28" t="s" s="2">
-        <v>240</v>
-      </c>
       <c r="AA28" t="s" s="2">
         <v>81</v>
       </c>
@@ -4993,7 +4989,7 @@
         <v>81</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -5008,24 +5004,24 @@
         <v>101</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5048,13 +5044,13 @@
         <v>81</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="L29" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>243</v>
-      </c>
-      <c r="M29" t="s" s="2">
-        <v>244</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5081,14 +5077,14 @@
         <v>81</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="Y29" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="Z29" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="Z29" t="s" s="2">
-        <v>245</v>
-      </c>
       <c r="AA29" t="s" s="2">
         <v>81</v>
       </c>
@@ -5105,7 +5101,7 @@
         <v>81</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -5123,25 +5119,25 @@
         <v>81</v>
       </c>
       <c r="AL29" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="AM29" t="s" s="2">
         <v>246</v>
       </c>
-      <c r="AM29" t="s" s="2">
+      <c r="AN29" t="s" s="2">
         <v>247</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>248</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -5160,16 +5156,16 @@
         <v>90</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="L30" t="s" s="2">
         <v>251</v>
       </c>
-      <c r="L30" t="s" s="2">
+      <c r="M30" t="s" s="2">
         <v>252</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>253</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>254</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5219,7 +5215,7 @@
         <v>81</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -5234,24 +5230,24 @@
         <v>101</v>
       </c>
       <c r="AK30" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="AL30" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="AL30" t="s" s="2">
+      <c r="AM30" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="AM30" t="s" s="2">
+      <c r="AN30" t="s" s="2">
         <v>257</v>
-      </c>
-      <c r="AN30" t="s" s="2">
-        <v>258</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5274,13 +5270,13 @@
         <v>90</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="L31" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="L31" t="s" s="2">
+      <c r="M31" t="s" s="2">
         <v>261</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>262</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5331,7 +5327,7 @@
         <v>81</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -5346,28 +5342,28 @@
         <v>101</v>
       </c>
       <c r="AK31" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="AL31" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="AM31" t="s" s="2">
         <v>263</v>
       </c>
-      <c r="AL31" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="AM31" t="s" s="2">
+      <c r="AN31" t="s" s="2">
         <v>264</v>
-      </c>
-      <c r="AN31" t="s" s="2">
-        <v>265</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5386,13 +5382,13 @@
         <v>81</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>268</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="M32" t="s" s="2">
         <v>269</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>270</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5443,7 +5439,7 @@
         <v>81</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -5458,10 +5454,10 @@
         <v>101</v>
       </c>
       <c r="AK32" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="AL32" t="s" s="2">
         <v>271</v>
-      </c>
-      <c r="AL32" t="s" s="2">
-        <v>272</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>81</v>
@@ -5472,10 +5468,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5498,13 +5494,13 @@
         <v>90</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>274</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>275</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5555,7 +5551,7 @@
         <v>81</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -5570,24 +5566,24 @@
         <v>101</v>
       </c>
       <c r="AK33" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="AL33" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="AL33" t="s" s="2">
+      <c r="AM33" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN33" t="s" s="2">
         <v>277</v>
-      </c>
-      <c r="AM33" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN33" t="s" s="2">
-        <v>278</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5610,13 +5606,13 @@
         <v>81</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="L34" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="L34" t="s" s="2">
+      <c r="M34" t="s" s="2">
         <v>181</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>182</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5667,7 +5663,7 @@
         <v>81</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -5685,7 +5681,7 @@
         <v>81</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>81</v>
@@ -5696,14 +5692,14 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -5725,13 +5721,13 @@
         <v>134</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="M35" t="s" s="2">
-        <v>186</v>
-      </c>
       <c r="N35" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5781,7 +5777,7 @@
         <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -5799,7 +5795,7 @@
         <v>81</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>81</v>
@@ -5810,14 +5806,14 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -5839,16 +5835,16 @@
         <v>134</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>190</v>
       </c>
-      <c r="M36" t="s" s="2">
-        <v>191</v>
-      </c>
       <c r="N36" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="O36" t="s" s="2">
         <v>151</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>152</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>81</v>
@@ -5897,7 +5893,7 @@
         <v>81</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -5926,10 +5922,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5952,16 +5948,16 @@
         <v>90</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>283</v>
       </c>
-      <c r="M37" t="s" s="2">
+      <c r="N37" t="s" s="2">
         <v>284</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>285</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -5987,13 +5983,13 @@
         <v>81</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>81</v>
@@ -6011,7 +6007,7 @@
         <v>81</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -6026,24 +6022,24 @@
         <v>101</v>
       </c>
       <c r="AK37" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="AL37" t="s" s="2">
         <v>287</v>
       </c>
-      <c r="AL37" t="s" s="2">
+      <c r="AM37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN37" t="s" s="2">
         <v>288</v>
-      </c>
-      <c r="AM37" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN37" t="s" s="2">
-        <v>289</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6066,13 +6062,13 @@
         <v>81</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6123,7 +6119,7 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -6141,21 +6137,21 @@
         <v>81</v>
       </c>
       <c r="AL38" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="AM38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN38" t="s" s="2">
         <v>293</v>
-      </c>
-      <c r="AM38" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN38" t="s" s="2">
-        <v>294</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6178,13 +6174,13 @@
         <v>90</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="L39" t="s" s="2">
         <v>296</v>
       </c>
-      <c r="L39" t="s" s="2">
+      <c r="M39" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>298</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6235,7 +6231,7 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -6250,24 +6246,24 @@
         <v>101</v>
       </c>
       <c r="AK39" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="AL39" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="AL39" t="s" s="2">
+      <c r="AM39" t="s" s="2">
         <v>300</v>
       </c>
-      <c r="AM39" t="s" s="2">
+      <c r="AN39" t="s" s="2">
         <v>301</v>
-      </c>
-      <c r="AN39" t="s" s="2">
-        <v>302</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6290,13 +6286,13 @@
         <v>90</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="L40" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="L40" t="s" s="2">
+      <c r="M40" t="s" s="2">
         <v>305</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>306</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6347,7 +6343,7 @@
         <v>81</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -6362,24 +6358,24 @@
         <v>101</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="AL40" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="AM40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN40" t="s" s="2">
         <v>307</v>
-      </c>
-      <c r="AM40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN40" t="s" s="2">
-        <v>308</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6402,16 +6398,16 @@
         <v>81</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="M41" t="s" s="2">
+      <c r="N41" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6461,7 +6457,7 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -6476,24 +6472,24 @@
         <v>101</v>
       </c>
       <c r="AK41" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="AL41" t="s" s="2">
         <v>313</v>
       </c>
-      <c r="AL41" t="s" s="2">
+      <c r="AM41" t="s" s="2">
         <v>314</v>
       </c>
-      <c r="AM41" t="s" s="2">
+      <c r="AN41" t="s" s="2">
         <v>315</v>
-      </c>
-      <c r="AN41" t="s" s="2">
-        <v>316</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6516,16 +6512,16 @@
         <v>81</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="L42" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="M42" t="s" s="2">
         <v>319</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>320</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>321</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6575,7 +6571,7 @@
         <v>81</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -6590,28 +6586,28 @@
         <v>101</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="AL42" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="AM42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN42" t="s" s="2">
         <v>322</v>
-      </c>
-      <c r="AM42" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN42" t="s" s="2">
-        <v>323</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6630,16 +6626,16 @@
         <v>90</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="N43" t="s" s="2">
         <v>327</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>328</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6668,11 +6664,11 @@
         <v>113</v>
       </c>
       <c r="Y43" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="Z43" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="Z43" t="s" s="2">
-        <v>330</v>
-      </c>
       <c r="AA43" t="s" s="2">
         <v>81</v>
       </c>
@@ -6689,7 +6685,7 @@
         <v>81</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -6704,28 +6700,28 @@
         <v>101</v>
       </c>
       <c r="AK43" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="AL43" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="AL43" t="s" s="2">
+      <c r="AM43" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="AM43" t="s" s="2">
+      <c r="AN43" t="s" s="2">
         <v>333</v>
-      </c>
-      <c r="AN43" t="s" s="2">
-        <v>334</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -6744,16 +6740,16 @@
         <v>90</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="L44" t="s" s="2">
         <v>336</v>
       </c>
-      <c r="L44" t="s" s="2">
-        <v>337</v>
-      </c>
       <c r="M44" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="N44" t="s" s="2">
         <v>327</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>328</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6803,7 +6799,7 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -6818,24 +6814,24 @@
         <v>101</v>
       </c>
       <c r="AK44" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="AL44" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="AL44" t="s" s="2">
+      <c r="AM44" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="AM44" t="s" s="2">
+      <c r="AN44" t="s" s="2">
         <v>333</v>
-      </c>
-      <c r="AN44" t="s" s="2">
-        <v>334</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6858,13 +6854,13 @@
         <v>90</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>339</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>340</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6915,7 +6911,7 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -6933,7 +6929,7 @@
         <v>81</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>81</v>
@@ -6944,10 +6940,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6970,13 +6966,13 @@
         <v>81</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="L46" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="L46" t="s" s="2">
+      <c r="M46" t="s" s="2">
         <v>181</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>182</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7027,7 +7023,7 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -7045,7 +7041,7 @@
         <v>81</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>81</v>
@@ -7056,14 +7052,14 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7085,13 +7081,13 @@
         <v>134</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="M47" t="s" s="2">
-        <v>186</v>
-      </c>
       <c r="N47" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7141,7 +7137,7 @@
         <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -7159,7 +7155,7 @@
         <v>81</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>81</v>
@@ -7170,14 +7166,14 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7199,16 +7195,16 @@
         <v>134</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>190</v>
       </c>
-      <c r="M48" t="s" s="2">
-        <v>191</v>
-      </c>
       <c r="N48" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="O48" t="s" s="2">
         <v>151</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>152</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>81</v>
@@ -7257,7 +7253,7 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -7286,14 +7282,14 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7312,16 +7308,16 @@
         <v>90</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="L49" t="s" s="2">
         <v>347</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="M49" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="M49" t="s" s="2">
-        <v>349</v>
-      </c>
       <c r="N49" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7371,7 +7367,7 @@
         <v>81</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>89</v>
@@ -7386,24 +7382,24 @@
         <v>101</v>
       </c>
       <c r="AK49" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="AL49" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="AL49" t="s" s="2">
+      <c r="AM49" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="AN49" t="s" s="2">
         <v>351</v>
-      </c>
-      <c r="AM49" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="AN49" t="s" s="2">
-        <v>352</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7426,13 +7422,13 @@
         <v>81</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>354</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>355</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7462,11 +7458,11 @@
         <v>113</v>
       </c>
       <c r="Y50" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="Z50" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="Z50" t="s" s="2">
-        <v>357</v>
-      </c>
       <c r="AA50" t="s" s="2">
         <v>81</v>
       </c>
@@ -7483,7 +7479,7 @@
         <v>81</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -7501,7 +7497,7 @@
         <v>81</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>81</v>
@@ -7512,10 +7508,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7538,13 +7534,13 @@
         <v>81</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="L51" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="L51" t="s" s="2">
+      <c r="M51" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>361</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7595,7 +7591,7 @@
         <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -7613,7 +7609,7 @@
         <v>81</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>81</v>
@@ -7624,10 +7620,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7650,16 +7646,16 @@
         <v>81</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="L52" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="L52" t="s" s="2">
+      <c r="M52" t="s" s="2">
         <v>365</v>
       </c>
-      <c r="M52" t="s" s="2">
+      <c r="N52" t="s" s="2">
         <v>366</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>367</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -7709,7 +7705,7 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -7727,7 +7723,7 @@
         <v>81</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>81</v>
@@ -7738,10 +7734,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7764,16 +7760,16 @@
         <v>81</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>370</v>
       </c>
-      <c r="M53" t="s" s="2">
+      <c r="N53" t="s" s="2">
         <v>371</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>372</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -7823,7 +7819,7 @@
         <v>81</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -7841,7 +7837,7 @@
         <v>81</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>81</v>
@@ -7852,10 +7848,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7878,13 +7874,13 @@
         <v>81</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="L54" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="L54" t="s" s="2">
+      <c r="M54" t="s" s="2">
         <v>181</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>182</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -7935,7 +7931,7 @@
         <v>81</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -7953,7 +7949,7 @@
         <v>81</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>81</v>
@@ -7964,14 +7960,14 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -7993,13 +7989,13 @@
         <v>134</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="M55" t="s" s="2">
-        <v>186</v>
-      </c>
       <c r="N55" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8049,7 +8045,7 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8067,7 +8063,7 @@
         <v>81</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>81</v>
@@ -8078,14 +8074,14 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8107,16 +8103,16 @@
         <v>134</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>190</v>
       </c>
-      <c r="M56" t="s" s="2">
-        <v>191</v>
-      </c>
       <c r="N56" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="O56" t="s" s="2">
         <v>151</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>152</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>81</v>
@@ -8165,7 +8161,7 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8194,10 +8190,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8220,13 +8216,13 @@
         <v>81</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>378</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>379</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8277,7 +8273,7 @@
         <v>81</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -8295,21 +8291,21 @@
         <v>81</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8332,13 +8328,13 @@
         <v>81</v>
       </c>
       <c r="K58" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="L58" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="L58" t="s" s="2">
+      <c r="M58" t="s" s="2">
         <v>383</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>384</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8389,7 +8385,7 @@
         <v>81</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -8407,7 +8403,7 @@
         <v>81</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>81</v>
@@ -8418,10 +8414,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8444,13 +8440,13 @@
         <v>81</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8480,11 +8476,11 @@
         <v>113</v>
       </c>
       <c r="Y59" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="Z59" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="Z59" t="s" s="2">
-        <v>388</v>
-      </c>
       <c r="AA59" t="s" s="2">
         <v>81</v>
       </c>
@@ -8501,7 +8497,7 @@
         <v>81</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -8519,21 +8515,21 @@
         <v>81</v>
       </c>
       <c r="AL59" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="AM59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN59" t="s" s="2">
         <v>389</v>
-      </c>
-      <c r="AM59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN59" t="s" s="2">
-        <v>390</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8556,13 +8552,13 @@
         <v>81</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>392</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>393</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8589,14 +8585,14 @@
         <v>81</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="Y60" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="Z60" t="s" s="2">
         <v>394</v>
       </c>
-      <c r="Z60" t="s" s="2">
-        <v>395</v>
-      </c>
       <c r="AA60" t="s" s="2">
         <v>81</v>
       </c>
@@ -8613,7 +8609,7 @@
         <v>81</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -8631,21 +8627,21 @@
         <v>81</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8668,19 +8664,19 @@
         <v>81</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="M61" t="s" s="2">
         <v>398</v>
       </c>
-      <c r="M61" t="s" s="2">
+      <c r="N61" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="N61" t="s" s="2">
+      <c r="O61" t="s" s="2">
         <v>400</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>401</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>81</v>
@@ -8705,14 +8701,14 @@
         <v>81</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="Y61" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="Z61" t="s" s="2">
         <v>402</v>
       </c>
-      <c r="Z61" t="s" s="2">
-        <v>403</v>
-      </c>
       <c r="AA61" t="s" s="2">
         <v>81</v>
       </c>
@@ -8729,7 +8725,7 @@
         <v>81</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -8747,21 +8743,21 @@
         <v>81</v>
       </c>
       <c r="AL61" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN61" t="s" s="2">
         <v>404</v>
-      </c>
-      <c r="AM61" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN61" t="s" s="2">
-        <v>405</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8784,13 +8780,13 @@
         <v>81</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="M62" t="s" s="2">
         <v>407</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>408</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -8820,11 +8816,11 @@
         <v>113</v>
       </c>
       <c r="Y62" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="Z62" t="s" s="2">
         <v>409</v>
       </c>
-      <c r="Z62" t="s" s="2">
-        <v>410</v>
-      </c>
       <c r="AA62" t="s" s="2">
         <v>81</v>
       </c>
@@ -8841,7 +8837,7 @@
         <v>81</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -8859,21 +8855,21 @@
         <v>81</v>
       </c>
       <c r="AL62" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="AM62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN62" t="s" s="2">
         <v>411</v>
-      </c>
-      <c r="AM62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN62" t="s" s="2">
-        <v>412</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8896,13 +8892,13 @@
         <v>81</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>414</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>415</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -8932,11 +8928,11 @@
         <v>113</v>
       </c>
       <c r="Y63" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="Z63" t="s" s="2">
         <v>416</v>
       </c>
-      <c r="Z63" t="s" s="2">
-        <v>417</v>
-      </c>
       <c r="AA63" t="s" s="2">
         <v>81</v>
       </c>
@@ -8953,7 +8949,7 @@
         <v>81</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -8971,21 +8967,21 @@
         <v>81</v>
       </c>
       <c r="AL63" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="AM63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN63" t="s" s="2">
         <v>418</v>
-      </c>
-      <c r="AM63" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN63" t="s" s="2">
-        <v>419</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9008,13 +9004,13 @@
         <v>81</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>422</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9065,7 +9061,7 @@
         <v>81</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -9083,21 +9079,21 @@
         <v>81</v>
       </c>
       <c r="AL64" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN64" t="s" s="2">
         <v>423</v>
-      </c>
-      <c r="AM64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN64" t="s" s="2">
-        <v>424</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9120,13 +9116,13 @@
         <v>81</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="L65" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="M65" t="s" s="2">
         <v>426</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>427</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9153,13 +9149,13 @@
         <v>81</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>81</v>
@@ -9177,7 +9173,7 @@
         <v>81</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -9195,21 +9191,21 @@
         <v>81</v>
       </c>
       <c r="AL65" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN65" t="s" s="2">
         <v>429</v>
-      </c>
-      <c r="AM65" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN65" t="s" s="2">
-        <v>430</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9232,16 +9228,16 @@
         <v>81</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="M66" t="s" s="2">
         <v>432</v>
       </c>
-      <c r="M66" t="s" s="2">
+      <c r="N66" t="s" s="2">
         <v>433</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>434</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -9291,7 +9287,7 @@
         <v>81</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -9309,7 +9305,7 @@
         <v>81</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>81</v>
@@ -9320,10 +9316,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9346,13 +9342,13 @@
         <v>81</v>
       </c>
       <c r="K67" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="L67" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="L67" t="s" s="2">
+      <c r="M67" t="s" s="2">
         <v>181</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>182</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9403,7 +9399,7 @@
         <v>81</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -9421,7 +9417,7 @@
         <v>81</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>81</v>
@@ -9432,14 +9428,14 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -9461,13 +9457,13 @@
         <v>134</v>
       </c>
       <c r="L68" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="M68" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="M68" t="s" s="2">
-        <v>186</v>
-      </c>
       <c r="N68" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -9517,7 +9513,7 @@
         <v>81</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -9535,7 +9531,7 @@
         <v>81</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>81</v>
@@ -9546,14 +9542,14 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -9575,16 +9571,16 @@
         <v>134</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="M69" t="s" s="2">
         <v>190</v>
       </c>
-      <c r="M69" t="s" s="2">
-        <v>191</v>
-      </c>
       <c r="N69" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="O69" t="s" s="2">
         <v>151</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>152</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>81</v>
@@ -9633,7 +9629,7 @@
         <v>81</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -9662,10 +9658,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9688,13 +9684,13 @@
         <v>81</v>
       </c>
       <c r="K70" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="L70" t="s" s="2">
         <v>440</v>
       </c>
-      <c r="L70" t="s" s="2">
+      <c r="M70" t="s" s="2">
         <v>441</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>442</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -9745,7 +9741,7 @@
         <v>81</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>89</v>
@@ -9760,24 +9756,24 @@
         <v>101</v>
       </c>
       <c r="AK70" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="AM70" t="s" s="2">
         <v>443</v>
       </c>
-      <c r="AL70" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="AM70" t="s" s="2">
+      <c r="AN70" t="s" s="2">
         <v>444</v>
-      </c>
-      <c r="AN70" t="s" s="2">
-        <v>445</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9803,13 +9799,13 @@
         <v>109</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="M71" t="s" s="2">
         <v>447</v>
       </c>
-      <c r="M71" t="s" s="2">
+      <c r="N71" t="s" s="2">
         <v>448</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>449</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -9835,14 +9831,14 @@
         <v>81</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Y71" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="Z71" t="s" s="2">
         <v>450</v>
       </c>
-      <c r="Z71" t="s" s="2">
-        <v>451</v>
-      </c>
       <c r="AA71" t="s" s="2">
         <v>81</v>
       </c>
@@ -9859,7 +9855,7 @@
         <v>81</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -9877,7 +9873,7 @@
         <v>81</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>81</v>
@@ -9888,10 +9884,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9914,16 +9910,16 @@
         <v>81</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="L72" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="M72" t="s" s="2">
         <v>454</v>
       </c>
-      <c r="M72" t="s" s="2">
+      <c r="N72" t="s" s="2">
         <v>455</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>456</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -9949,14 +9945,14 @@
         <v>81</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="Y72" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="Z72" t="s" s="2">
         <v>457</v>
       </c>
-      <c r="Z72" t="s" s="2">
-        <v>458</v>
-      </c>
       <c r="AA72" t="s" s="2">
         <v>81</v>
       </c>
@@ -9973,7 +9969,7 @@
         <v>81</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -10002,10 +9998,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10028,13 +10024,13 @@
         <v>81</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10085,7 +10081,7 @@
         <v>81</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
@@ -10103,7 +10099,7 @@
         <v>81</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>81</v>
@@ -10114,10 +10110,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10140,13 +10136,13 @@
         <v>81</v>
       </c>
       <c r="K74" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="L74" t="s" s="2">
         <v>462</v>
       </c>
-      <c r="L74" t="s" s="2">
+      <c r="M74" t="s" s="2">
         <v>463</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>464</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -10197,7 +10193,7 @@
         <v>81</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -10212,24 +10208,24 @@
         <v>101</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="AL74" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN74" t="s" s="2">
         <v>465</v>
-      </c>
-      <c r="AM74" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN74" t="s" s="2">
-        <v>466</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10252,16 +10248,16 @@
         <v>81</v>
       </c>
       <c r="K75" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="L75" t="s" s="2">
         <v>468</v>
       </c>
-      <c r="L75" t="s" s="2">
+      <c r="M75" t="s" s="2">
         <v>469</v>
       </c>
-      <c r="M75" t="s" s="2">
+      <c r="N75" t="s" s="2">
         <v>470</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>471</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -10311,7 +10307,7 @@
         <v>81</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
@@ -10326,10 +10322,10 @@
         <v>101</v>
       </c>
       <c r="AK75" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="AL75" t="s" s="2">
         <v>472</v>
-      </c>
-      <c r="AL75" t="s" s="2">
-        <v>473</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>81</v>

--- a/jpcore-r4/develop-kohetest/StructureDefinition-jp-encounter.xlsx
+++ b/jpcore-r4/develop-kohetest/StructureDefinition-jp-encounter.xlsx
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Encounter|4.0.1</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Encounter</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -369,7 +369,7 @@
     <t>人間の言語。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/languages</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -663,7 +663,7 @@
     <t>受療行動の分類。</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/ValueSet/v3-ActEncounterCode|3.0.0</t>
+    <t>http://terminology.hl7.org/ValueSet/v3-ActEncounterCode</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=SUBJ].source[classCode=LIST].code</t>
@@ -737,7 +737,7 @@
     <t>受療行動のタイプ。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/encounter-type|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/encounter-type</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -761,7 +761,7 @@
     <t>提供されるサービスの広範な分類。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/service-type|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/service-type</t>
   </si>
   <si>
     <t>PV1-10</t>
@@ -776,7 +776,7 @@
     <t>受療行動の緊急性を示します。</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/ValueSet/v3-ActPriority|3.0.0</t>
+    <t>http://terminology.hl7.org/ValueSet/v3-ActPriority</t>
   </si>
   <si>
     <t>.priorityCode</t>
@@ -795,7 +795,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|1.3.0-dev|Group|4.0.1)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|Group)
 </t>
   </si>
   <si>
@@ -823,7 +823,7 @@
     <t>Encounter.episodeOfCare</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(EpisodeOfCare|4.0.1)
+    <t xml:space="preserve">Reference(EpisodeOfCare)
 </t>
   </si>
   <si>
@@ -849,7 +849,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(ServiceRequest|4.0.1)
+    <t xml:space="preserve">Reference(ServiceRequest)
 </t>
   </si>
   <si>
@@ -904,7 +904,7 @@
     <t>参加者タイプは、個人がどのようにエンカウントに参加するかを示します。それには、非開業者の参加者が含まれ、開業者にとってはこのエンカウントの文脈でアクションタイプを説明することが含まれます（例：入院医師、診療医師、翻訳者、相談医師）。これは、雇用、教育、免許などの用語から派生した機能的な役割である開業者の役割とは異なります。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/encounter-participant-type|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/encounter-participant-type</t>
   </si>
   <si>
     <t>Event.performer.function</t>
@@ -934,7 +934,7 @@
     <t>Encounter.participant.individual</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole|1.3.0-dev|RelatedPerson|4.0.1)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole|RelatedPerson)
 </t>
   </si>
   <si>
@@ -959,7 +959,7 @@
     <t>Encounter.appointment</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Appointment|4.0.1)
+    <t xml:space="preserve">Reference(Appointment)
 </t>
   </si>
   <si>
@@ -1040,7 +1040,7 @@
     <t>受療行動が起こる理由。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/encounter-reason|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/encounter-reason</t>
   </si>
   <si>
     <t>Event.reasonCode</t>
@@ -1058,7 +1058,7 @@
     <t>Encounter.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Condition|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Condition_Diagnosis|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Procedure|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Common|1.3.0-dev|ImmunizationRecommendation|4.0.1)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Condition|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Condition_Diagnosis|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Procedure|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Common|ImmunizationRecommendation)
 </t>
   </si>
   <si>
@@ -1093,7 +1093,7 @@
 discharge diagnosisindication</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Condition|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Condition_Diagnosis|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Procedure|1.3.0-dev)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Condition|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Condition_Diagnosis|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Procedure)
 </t>
   </si>
   <si>
@@ -1124,7 +1124,7 @@
     <t>この状態が表す診断のタイプ。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/diagnosis-role|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/diagnosis-role</t>
   </si>
   <si>
     <t>Encounter.diagnosis.rank</t>
@@ -1146,7 +1146,7 @@
     <t>Encounter.account</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Account|4.0.1)
+    <t xml:space="preserve">Reference(Account)
 </t>
   </si>
   <si>
@@ -1202,7 +1202,7 @@
     <t>Encounter.hospitalization.origin</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Location|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization|1.3.0-dev)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Location|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization)
 </t>
   </si>
   <si>
@@ -1221,7 +1221,7 @@
     <t>患者がどこから入院したのか（医師の紹介、転院）</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/encounter-admit-source|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/encounter-admit-source</t>
   </si>
   <si>
     <t>.admissionReferralSourceCode</t>
@@ -1242,7 +1242,7 @@
     <t>この入院の再入院の理由。</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/ValueSet/v2-0092|2.0.0</t>
+    <t>http://terminology.hl7.org/ValueSet/v2-0092</t>
   </si>
   <si>
     <t>PV1-13</t>
@@ -1266,7 +1266,7 @@
     <t>食品の好みを考慮して、医療、文化、倫理的観点から、提供要件に対応することができます。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/encounter-diet|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/encounter-diet</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode=COMP].target[classCode=SBADM, moodCode=EVN, code="diet"]</t>
@@ -1287,7 +1287,7 @@
     <t>特別なおもてなし。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/encounter-special-courtesy|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/encounter-special-courtesy</t>
   </si>
   <si>
     <t>.specialCourtesiesCode</t>
@@ -1308,7 +1308,7 @@
     <t>特別な手配。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/encounter-special-arrangements|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/encounter-special-arrangements</t>
   </si>
   <si>
     <t>.specialArrangementCode</t>
@@ -1341,7 +1341,7 @@
     <t>退院後の場所のカテゴリーまたは種類。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/encounter-discharge-disposition|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/encounter-discharge-disposition</t>
   </si>
   <si>
     <t>.dischargeDispositionCode</t>
@@ -1377,7 +1377,7 @@
     <t>Encounter.location.location</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Location|1.3.0-dev)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Location)
 </t>
   </si>
   <si>
@@ -1433,7 +1433,7 @@
     <t>場所の実体形態。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/location-physical-type|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/location-physical-type</t>
   </si>
   <si>
     <t>Encounter.location.period</t>
@@ -1445,7 +1445,7 @@
     <t>Encounter.serviceProvider</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization|1.3.0-dev)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization)
 </t>
   </si>
   <si>
@@ -1464,7 +1464,7 @@
     <t>Encounter.partOf</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Encounter|1.3.0-dev)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Encounter)
 </t>
   </si>
   <si>
@@ -1797,7 +1797,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="230.390625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1812,7 +1812,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="40.51171875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="52.75390625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="48.2265625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>

--- a/jpcore-r4/develop-kohetest/StructureDefinition-jp-encounter.xlsx
+++ b/jpcore-r4/develop-kohetest/StructureDefinition-jp-encounter.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2716" uniqueCount="473">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2716" uniqueCount="474">
   <si>
     <t>Property</t>
   </si>
@@ -460,15 +460,19 @@
     <t>associatedEncounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {encounter-associatedEncounter|5.2.0}
+    <t xml:space="preserve">Extension {encounter-associatedEncounter|4.0.1}
 </t>
   </si>
   <si>
     <t>関連するEncounter</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>Encounter.modifierExtension</t>
@@ -2950,10 +2954,10 @@
         <v>80</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>81</v>
+        <v>145</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>81</v>
@@ -2970,14 +2974,14 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
@@ -2999,16 +3003,16 @@
         <v>134</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O11" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>81</v>
@@ -3057,7 +3061,7 @@
         <v>81</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>79</v>
@@ -3086,10 +3090,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3112,13 +3116,13 @@
         <v>90</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -3169,7 +3173,7 @@
         <v>81</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>79</v>
@@ -3184,24 +3188,24 @@
         <v>101</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3227,13 +3231,13 @@
         <v>109</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3259,13 +3263,13 @@
         <v>81</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>81</v>
@@ -3283,7 +3287,7 @@
         <v>81</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>89</v>
@@ -3298,24 +3302,24 @@
         <v>101</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3338,16 +3342,16 @@
         <v>81</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3397,7 +3401,7 @@
         <v>81</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>79</v>
@@ -3415,7 +3419,7 @@
         <v>81</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AM14" t="s" s="2">
         <v>81</v>
@@ -3426,10 +3430,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3452,13 +3456,13 @@
         <v>81</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -3509,7 +3513,7 @@
         <v>81</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>79</v>
@@ -3527,7 +3531,7 @@
         <v>81</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>81</v>
@@ -3538,14 +3542,14 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3567,13 +3571,13 @@
         <v>134</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3623,7 +3627,7 @@
         <v>81</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
@@ -3641,7 +3645,7 @@
         <v>81</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>81</v>
@@ -3652,14 +3656,14 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3681,16 +3685,16 @@
         <v>134</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>81</v>
@@ -3739,7 +3743,7 @@
         <v>81</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -3768,10 +3772,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3797,13 +3801,13 @@
         <v>109</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3829,13 +3833,13 @@
         <v>81</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>81</v>
@@ -3853,7 +3857,7 @@
         <v>81</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>89</v>
@@ -3871,7 +3875,7 @@
         <v>81</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>81</v>
@@ -3882,10 +3886,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3908,16 +3912,16 @@
         <v>81</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3967,7 +3971,7 @@
         <v>81</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>89</v>
@@ -3985,7 +3989,7 @@
         <v>81</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>81</v>
@@ -3996,10 +4000,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4022,16 +4026,16 @@
         <v>90</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4057,13 +4061,13 @@
         <v>81</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>81</v>
@@ -4081,7 +4085,7 @@
         <v>81</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>89</v>
@@ -4099,21 +4103,21 @@
         <v>81</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4136,13 +4140,13 @@
         <v>81</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4193,7 +4197,7 @@
         <v>81</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -4211,7 +4215,7 @@
         <v>81</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>81</v>
@@ -4222,10 +4226,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4248,13 +4252,13 @@
         <v>81</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4305,7 +4309,7 @@
         <v>81</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -4323,7 +4327,7 @@
         <v>81</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>81</v>
@@ -4334,14 +4338,14 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -4363,13 +4367,13 @@
         <v>134</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4419,7 +4423,7 @@
         <v>81</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -4437,7 +4441,7 @@
         <v>81</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>81</v>
@@ -4448,14 +4452,14 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4477,16 +4481,16 @@
         <v>134</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>81</v>
@@ -4535,7 +4539,7 @@
         <v>81</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -4564,10 +4568,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4590,16 +4594,16 @@
         <v>81</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4625,13 +4629,13 @@
         <v>81</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>81</v>
@@ -4649,7 +4653,7 @@
         <v>81</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>89</v>
@@ -4667,7 +4671,7 @@
         <v>81</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>81</v>
@@ -4678,10 +4682,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4704,16 +4708,16 @@
         <v>81</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4763,7 +4767,7 @@
         <v>81</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>89</v>
@@ -4781,7 +4785,7 @@
         <v>81</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>81</v>
@@ -4792,10 +4796,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4818,16 +4822,16 @@
         <v>90</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -4853,13 +4857,13 @@
         <v>81</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>81</v>
@@ -4877,7 +4881,7 @@
         <v>81</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -4892,24 +4896,24 @@
         <v>101</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4932,13 +4936,13 @@
         <v>90</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4965,13 +4969,13 @@
         <v>81</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>81</v>
@@ -4989,7 +4993,7 @@
         <v>81</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -5004,24 +5008,24 @@
         <v>101</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5044,13 +5048,13 @@
         <v>81</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5077,13 +5081,13 @@
         <v>81</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>81</v>
@@ -5101,7 +5105,7 @@
         <v>81</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -5119,25 +5123,25 @@
         <v>81</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -5156,16 +5160,16 @@
         <v>90</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5215,7 +5219,7 @@
         <v>81</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -5230,24 +5234,24 @@
         <v>101</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5270,13 +5274,13 @@
         <v>90</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5327,7 +5331,7 @@
         <v>81</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -5342,28 +5346,28 @@
         <v>101</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5382,13 +5386,13 @@
         <v>81</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5439,7 +5443,7 @@
         <v>81</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -5454,10 +5458,10 @@
         <v>101</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>81</v>
@@ -5468,10 +5472,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5494,13 +5498,13 @@
         <v>90</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5551,7 +5555,7 @@
         <v>81</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -5566,24 +5570,24 @@
         <v>101</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5606,13 +5610,13 @@
         <v>81</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5663,7 +5667,7 @@
         <v>81</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -5681,7 +5685,7 @@
         <v>81</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>81</v>
@@ -5692,14 +5696,14 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -5721,13 +5725,13 @@
         <v>134</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5777,7 +5781,7 @@
         <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -5795,7 +5799,7 @@
         <v>81</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>81</v>
@@ -5806,14 +5810,14 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -5835,16 +5839,16 @@
         <v>134</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>81</v>
@@ -5893,7 +5897,7 @@
         <v>81</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -5922,10 +5926,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5948,16 +5952,16 @@
         <v>90</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -5983,13 +5987,13 @@
         <v>81</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>81</v>
@@ -6007,7 +6011,7 @@
         <v>81</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -6022,24 +6026,24 @@
         <v>101</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6062,13 +6066,13 @@
         <v>81</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6119,7 +6123,7 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -6137,21 +6141,21 @@
         <v>81</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6174,13 +6178,13 @@
         <v>90</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6231,7 +6235,7 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -6246,24 +6250,24 @@
         <v>101</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6286,13 +6290,13 @@
         <v>90</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6343,7 +6347,7 @@
         <v>81</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -6358,24 +6362,24 @@
         <v>101</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6398,16 +6402,16 @@
         <v>81</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6457,7 +6461,7 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -6472,24 +6476,24 @@
         <v>101</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6512,16 +6516,16 @@
         <v>81</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6571,7 +6575,7 @@
         <v>81</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -6586,28 +6590,28 @@
         <v>101</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6626,16 +6630,16 @@
         <v>90</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6664,10 +6668,10 @@
         <v>113</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>81</v>
@@ -6685,7 +6689,7 @@
         <v>81</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -6700,28 +6704,28 @@
         <v>101</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -6740,16 +6744,16 @@
         <v>90</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6799,7 +6803,7 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -6814,24 +6818,24 @@
         <v>101</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6854,13 +6858,13 @@
         <v>90</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6911,7 +6915,7 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -6929,7 +6933,7 @@
         <v>81</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>81</v>
@@ -6940,10 +6944,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6966,13 +6970,13 @@
         <v>81</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7023,7 +7027,7 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -7041,7 +7045,7 @@
         <v>81</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>81</v>
@@ -7052,14 +7056,14 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7081,13 +7085,13 @@
         <v>134</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7137,7 +7141,7 @@
         <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -7155,7 +7159,7 @@
         <v>81</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>81</v>
@@ -7166,14 +7170,14 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7195,16 +7199,16 @@
         <v>134</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>81</v>
@@ -7253,7 +7257,7 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -7282,14 +7286,14 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7308,16 +7312,16 @@
         <v>90</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7367,7 +7371,7 @@
         <v>81</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>89</v>
@@ -7382,24 +7386,24 @@
         <v>101</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7422,13 +7426,13 @@
         <v>81</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7458,10 +7462,10 @@
         <v>113</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>81</v>
@@ -7479,7 +7483,7 @@
         <v>81</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -7497,7 +7501,7 @@
         <v>81</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>81</v>
@@ -7508,10 +7512,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7534,13 +7538,13 @@
         <v>81</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7591,7 +7595,7 @@
         <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -7609,7 +7613,7 @@
         <v>81</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>81</v>
@@ -7620,10 +7624,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7646,16 +7650,16 @@
         <v>81</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -7705,7 +7709,7 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -7723,7 +7727,7 @@
         <v>81</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>81</v>
@@ -7734,10 +7738,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7760,16 +7764,16 @@
         <v>81</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -7819,7 +7823,7 @@
         <v>81</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -7837,7 +7841,7 @@
         <v>81</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>81</v>
@@ -7848,10 +7852,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7874,13 +7878,13 @@
         <v>81</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -7931,7 +7935,7 @@
         <v>81</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -7949,7 +7953,7 @@
         <v>81</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>81</v>
@@ -7960,14 +7964,14 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -7989,13 +7993,13 @@
         <v>134</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8045,7 +8049,7 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8063,7 +8067,7 @@
         <v>81</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>81</v>
@@ -8074,14 +8078,14 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8103,16 +8107,16 @@
         <v>134</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>81</v>
@@ -8161,7 +8165,7 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8190,10 +8194,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8216,13 +8220,13 @@
         <v>81</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8273,7 +8277,7 @@
         <v>81</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -8291,21 +8295,21 @@
         <v>81</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8328,13 +8332,13 @@
         <v>81</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8385,7 +8389,7 @@
         <v>81</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -8403,7 +8407,7 @@
         <v>81</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>81</v>
@@ -8414,10 +8418,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8440,13 +8444,13 @@
         <v>81</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8476,28 +8480,28 @@
         <v>113</v>
       </c>
       <c r="Y59" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF59" t="s" s="2">
         <v>386</v>
-      </c>
-      <c r="Z59" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="AA59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF59" t="s" s="2">
-        <v>385</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -8515,21 +8519,21 @@
         <v>81</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8552,13 +8556,13 @@
         <v>81</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8585,13 +8589,13 @@
         <v>81</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>81</v>
@@ -8609,7 +8613,7 @@
         <v>81</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -8627,21 +8631,21 @@
         <v>81</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8664,19 +8668,19 @@
         <v>81</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>81</v>
@@ -8701,13 +8705,13 @@
         <v>81</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>81</v>
@@ -8725,7 +8729,7 @@
         <v>81</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -8743,21 +8747,21 @@
         <v>81</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8780,13 +8784,13 @@
         <v>81</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -8816,10 +8820,10 @@
         <v>113</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>81</v>
@@ -8837,7 +8841,7 @@
         <v>81</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -8855,21 +8859,21 @@
         <v>81</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8892,13 +8896,13 @@
         <v>81</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -8928,10 +8932,10 @@
         <v>113</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>81</v>
@@ -8949,7 +8953,7 @@
         <v>81</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -8967,21 +8971,21 @@
         <v>81</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9004,13 +9008,13 @@
         <v>81</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9061,7 +9065,7 @@
         <v>81</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -9079,21 +9083,21 @@
         <v>81</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9116,13 +9120,13 @@
         <v>81</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9149,31 +9153,31 @@
         <v>81</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Y65" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF65" t="s" s="2">
         <v>425</v>
-      </c>
-      <c r="Z65" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="AA65" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB65" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC65" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD65" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE65" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF65" t="s" s="2">
-        <v>424</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -9191,21 +9195,21 @@
         <v>81</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9228,16 +9232,16 @@
         <v>81</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -9287,7 +9291,7 @@
         <v>81</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -9305,7 +9309,7 @@
         <v>81</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>81</v>
@@ -9316,10 +9320,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9342,13 +9346,13 @@
         <v>81</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9399,7 +9403,7 @@
         <v>81</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -9417,7 +9421,7 @@
         <v>81</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>81</v>
@@ -9428,14 +9432,14 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -9457,13 +9461,13 @@
         <v>134</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -9513,7 +9517,7 @@
         <v>81</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -9531,7 +9535,7 @@
         <v>81</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>81</v>
@@ -9542,14 +9546,14 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -9571,16 +9575,16 @@
         <v>134</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>81</v>
@@ -9629,7 +9633,7 @@
         <v>81</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -9658,10 +9662,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9684,13 +9688,13 @@
         <v>81</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -9741,7 +9745,7 @@
         <v>81</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>89</v>
@@ -9756,24 +9760,24 @@
         <v>101</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9799,13 +9803,13 @@
         <v>109</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -9831,13 +9835,13 @@
         <v>81</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>81</v>
@@ -9855,7 +9859,7 @@
         <v>81</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -9873,7 +9877,7 @@
         <v>81</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>81</v>
@@ -9884,10 +9888,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9910,16 +9914,16 @@
         <v>81</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -9945,13 +9949,13 @@
         <v>81</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>81</v>
@@ -9969,7 +9973,7 @@
         <v>81</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -9998,10 +10002,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10024,13 +10028,13 @@
         <v>81</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10081,7 +10085,7 @@
         <v>81</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
@@ -10099,7 +10103,7 @@
         <v>81</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>81</v>
@@ -10110,10 +10114,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10136,13 +10140,13 @@
         <v>81</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -10193,7 +10197,7 @@
         <v>81</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -10208,24 +10212,24 @@
         <v>101</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10248,16 +10252,16 @@
         <v>81</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -10307,7 +10311,7 @@
         <v>81</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
@@ -10322,10 +10326,10 @@
         <v>101</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>81</v>
